--- a/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
+++ b/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LocalFiles\p57448\CargoUIAutomation\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\IdeaProjects\Cargo\CargoUIAutomationNew\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFFA5690-8281-4F34-806F-F4CECC87A91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9805FD-A080-4DF8-80C8-2BFA470AB6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="2" xr2:uid="{1AB005B2-AFEC-3B46-93EF-50FA3BE3C5FF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="18" xr2:uid="{1AB005B2-AFEC-3B46-93EF-50FA3BE3C5FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="14" r:id="rId1"/>
@@ -40,32 +40,24 @@
     <definedName name="DataColumnRange">MasterSheet!$A$2:$A$129</definedName>
     <definedName name="dataRowRange">MasterSheet!$B$1:$AL$1</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -80,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5270" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5271" uniqueCount="409">
   <si>
     <t>LoginCredentials</t>
   </si>
@@ -1313,9 +1305,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1640,9 +1639,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1650,25 +1649,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1676,25 +1675,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1704,14 +1703,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1720,46 +1719,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1768,7 +1767,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1819,21 +1818,21 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1841,6 +1840,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2165,12 +2167,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4D241A-A8EF-49D1-8679-699235E5685A}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.796875" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.83203125" style="11"/>
+    <col min="4" max="16384" width="8.796875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2240,16 +2242,16 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0B29DB4-834B-3D43-AE5D-83E0EA72CBB8}">
   <dimension ref="A1:AL15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="101" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.58203125" customWidth="1"/>
+    <col min="3" max="3" width="27.59765625" customWidth="1"/>
     <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.296875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="17.58203125" customWidth="1"/>
+    <col min="38" max="38" width="17.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" s="11" customFormat="1">
@@ -2368,7 +2370,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="16.5">
+    <row r="2" spans="1:38" ht="16.8">
       <c r="A2" s="32" t="s">
         <v>278</v>
       </c>
@@ -2519,7 +2521,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="16.5">
+    <row r="3" spans="1:38" ht="16.8">
       <c r="A3" s="32" t="s">
         <v>279</v>
       </c>
@@ -2670,7 +2672,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="16.5">
+    <row r="4" spans="1:38" ht="16.8">
       <c r="A4" s="32" t="s">
         <v>280</v>
       </c>
@@ -2821,7 +2823,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="16.5">
+    <row r="5" spans="1:38" ht="16.8">
       <c r="A5" s="32" t="s">
         <v>281</v>
       </c>
@@ -2972,7 +2974,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="16.5">
+    <row r="6" spans="1:38" ht="16.8">
       <c r="A6" s="32" t="s">
         <v>282</v>
       </c>
@@ -3123,7 +3125,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="16.5">
+    <row r="7" spans="1:38" ht="16.8">
       <c r="A7" s="32" t="s">
         <v>283</v>
       </c>
@@ -3274,7 +3276,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="16.5">
+    <row r="8" spans="1:38" ht="16.8">
       <c r="A8" s="32" t="s">
         <v>284</v>
       </c>
@@ -3425,7 +3427,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="16.5">
+    <row r="9" spans="1:38" ht="16.8">
       <c r="A9" s="32" t="s">
         <v>285</v>
       </c>
@@ -3576,7 +3578,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="16.5">
+    <row r="10" spans="1:38" ht="16.8">
       <c r="A10" s="32" t="s">
         <v>286</v>
       </c>
@@ -3727,7 +3729,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="16.5">
+    <row r="11" spans="1:38" ht="16.8">
       <c r="A11" s="32" t="s">
         <v>287</v>
       </c>
@@ -3878,7 +3880,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="16.5">
+    <row r="12" spans="1:38" ht="16.8">
       <c r="A12" s="32" t="s">
         <v>288</v>
       </c>
@@ -4029,7 +4031,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="16.5">
+    <row r="13" spans="1:38" ht="16.8">
       <c r="A13" s="32" t="s">
         <v>289</v>
       </c>
@@ -4180,7 +4182,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="16.5">
+    <row r="14" spans="1:38" ht="16.8">
       <c r="A14" s="32" t="s">
         <v>290</v>
       </c>
@@ -4331,7 +4333,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="16.5">
+    <row r="15" spans="1:38" ht="16.8">
       <c r="A15" s="32" t="s">
         <v>291</v>
       </c>
@@ -4495,18 +4497,18 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7508C757-379C-BD45-982F-A9AA36397E0D}">
   <dimension ref="A1:Z36"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="51.83203125" customWidth="1"/>
+    <col min="1" max="1" width="51.796875" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="37.08203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.08203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.08203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27.08203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="37.09765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.09765625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27.09765625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -7119,49 +7121,49 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6A7DA2-FEB7-B54D-86C6-DFEA37D68DD1}">
   <dimension ref="A1:AM7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="102" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.58203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.296875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.296875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.5" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="19" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="37.08203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.58203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.08203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="37.09765625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.09765625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="28" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.08203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="24.08203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="29.08203125" customWidth="1"/>
-    <col min="32" max="33" width="8.58203125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.08203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="32.296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.09765625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="24.09765625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="29.09765625" customWidth="1"/>
+    <col min="32" max="33" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.09765625" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6.08203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.33203125" customWidth="1"/>
-    <col min="39" max="39" width="21.08203125" customWidth="1"/>
+    <col min="36" max="36" width="6.09765625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.296875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.296875" customWidth="1"/>
+    <col min="39" max="39" width="21.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="11" customFormat="1" ht="16" thickBot="1">
+    <row r="1" spans="1:39" s="11" customFormat="1" ht="16.2" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>118</v>
       </c>
@@ -7280,7 +7282,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="17" thickBot="1">
+    <row r="2" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A2" s="64" t="s">
         <v>306</v>
       </c>
@@ -7435,7 +7437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="17" thickBot="1">
+    <row r="3" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A3" s="64" t="s">
         <v>307</v>
       </c>
@@ -7590,7 +7592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="17" thickBot="1">
+    <row r="4" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A4" s="64" t="s">
         <v>308</v>
       </c>
@@ -7745,7 +7747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="17" thickBot="1">
+    <row r="5" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A5" s="64" t="s">
         <v>309</v>
       </c>
@@ -7900,7 +7902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="17" thickBot="1">
+    <row r="6" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A6" s="64" t="s">
         <v>310</v>
       </c>
@@ -8055,7 +8057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="17" thickBot="1">
+    <row r="7" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A7" s="64" t="s">
         <v>311</v>
       </c>
@@ -8221,18 +8223,18 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78402954-2B6D-C042-9263-9F192091C8D5}">
   <dimension ref="A1:AN7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="62.83203125" customWidth="1"/>
+    <col min="1" max="1" width="62.796875" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.796875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="16" customWidth="1"/>
-    <col min="40" max="40" width="13.33203125" customWidth="1"/>
+    <col min="40" max="40" width="13.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="11" customFormat="1" ht="16" thickBot="1">
+    <row r="1" spans="1:40" s="11" customFormat="1" ht="16.2" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>118</v>
       </c>
@@ -8354,7 +8356,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="17" thickBot="1">
+    <row r="2" spans="1:40" ht="17.399999999999999" thickBot="1">
       <c r="A2" s="65" t="s">
         <v>302</v>
       </c>
@@ -8513,7 +8515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:40" ht="17" thickBot="1">
+    <row r="3" spans="1:40" ht="17.399999999999999" thickBot="1">
       <c r="A3" s="65" t="s">
         <v>303</v>
       </c>
@@ -8672,7 +8674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:40" ht="17" thickBot="1">
+    <row r="4" spans="1:40" ht="17.399999999999999" thickBot="1">
       <c r="A4" s="65" t="s">
         <v>304</v>
       </c>
@@ -8831,7 +8833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:40" ht="17" thickBot="1">
+    <row r="5" spans="1:40" ht="17.399999999999999" thickBot="1">
       <c r="A5" s="65" t="s">
         <v>305</v>
       </c>
@@ -8990,7 +8992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:40" ht="17" thickBot="1">
+    <row r="6" spans="1:40" ht="17.399999999999999" thickBot="1">
       <c r="A6" s="65" t="s">
         <v>398</v>
       </c>
@@ -9149,7 +9151,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:40" ht="17" thickBot="1">
+    <row r="7" spans="1:40" ht="17.399999999999999" thickBot="1">
       <c r="A7" s="65" t="s">
         <v>399</v>
       </c>
@@ -9319,48 +9321,48 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85CBF01-6F2F-C544-96AC-B46CDE75B137}">
   <dimension ref="A1:AL13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="89.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="89.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.59765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.08203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.09765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.08203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.08203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.08203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="37.08203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="20.08203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.69921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.09765625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="37.09765625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.19921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.09765625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="28" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="32.25" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="21.58203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.25" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.58203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="32.19921875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="21.59765625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.296875" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="6.59765625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.296875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="11" customFormat="1" ht="16" thickBot="1">
+    <row r="1" spans="1:38" s="11" customFormat="1" ht="16.2" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>118</v>
       </c>
@@ -9476,7 +9478,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="17" thickBot="1">
+    <row r="2" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A2" s="69" t="s">
         <v>375</v>
       </c>
@@ -9627,7 +9629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="17" thickBot="1">
+    <row r="3" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A3" s="70" t="s">
         <v>376</v>
       </c>
@@ -9778,7 +9780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="17" thickBot="1">
+    <row r="4" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A4" s="70" t="s">
         <v>377</v>
       </c>
@@ -9929,7 +9931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="17" thickBot="1">
+    <row r="5" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A5" s="70" t="s">
         <v>378</v>
       </c>
@@ -10080,7 +10082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="17" thickBot="1">
+    <row r="6" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A6" s="70" t="s">
         <v>379</v>
       </c>
@@ -10231,7 +10233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="17" thickBot="1">
+    <row r="7" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A7" s="70" t="s">
         <v>380</v>
       </c>
@@ -10382,7 +10384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="17" thickBot="1">
+    <row r="8" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A8" s="70" t="s">
         <v>381</v>
       </c>
@@ -10533,7 +10535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="17" thickBot="1">
+    <row r="9" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A9" s="70" t="s">
         <v>382</v>
       </c>
@@ -10684,7 +10686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="17" thickBot="1">
+    <row r="10" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A10" s="70" t="s">
         <v>383</v>
       </c>
@@ -10835,7 +10837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="17" thickBot="1">
+    <row r="11" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A11" s="70" t="s">
         <v>384</v>
       </c>
@@ -10986,7 +10988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="17" thickBot="1">
+    <row r="12" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A12" s="70" t="s">
         <v>385</v>
       </c>
@@ -11137,7 +11139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="17" thickBot="1">
+    <row r="13" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A13" s="70" t="s">
         <v>386</v>
       </c>
@@ -11300,19 +11302,19 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFFF123C-E07E-C740-AE81-4E891CD59C3F}">
   <dimension ref="A1:AM11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="92.58203125" customWidth="1"/>
-    <col min="3" max="3" width="46.08203125" customWidth="1"/>
-    <col min="4" max="4" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="92.59765625" customWidth="1"/>
+    <col min="3" max="3" width="46.09765625" customWidth="1"/>
+    <col min="4" max="4" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42.58203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.08203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42.59765625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.09765625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="11" customFormat="1" ht="16" thickBot="1">
+    <row r="1" spans="1:39" s="11" customFormat="1" ht="16.2" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>118</v>
       </c>
@@ -11431,7 +11433,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="17" thickBot="1">
+    <row r="2" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A2" t="s">
         <v>388</v>
       </c>
@@ -11586,7 +11588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="17" thickBot="1">
+    <row r="3" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A3" t="s">
         <v>389</v>
       </c>
@@ -11741,7 +11743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="17" thickBot="1">
+    <row r="4" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A4" t="s">
         <v>390</v>
       </c>
@@ -11896,7 +11898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="17" thickBot="1">
+    <row r="5" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A5" t="s">
         <v>391</v>
       </c>
@@ -12051,7 +12053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="17" thickBot="1">
+    <row r="6" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A6" t="s">
         <v>392</v>
       </c>
@@ -12206,7 +12208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="17" thickBot="1">
+    <row r="7" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A7" t="s">
         <v>393</v>
       </c>
@@ -12361,7 +12363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="17" thickBot="1">
+    <row r="8" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A8" t="s">
         <v>394</v>
       </c>
@@ -12516,7 +12518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:39" ht="17" thickBot="1">
+    <row r="9" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A9" t="s">
         <v>395</v>
       </c>
@@ -12671,7 +12673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="17" thickBot="1">
+    <row r="10" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A10" t="s">
         <v>396</v>
       </c>
@@ -12826,7 +12828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="17" thickBot="1">
+    <row r="11" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A11" t="s">
         <v>397</v>
       </c>
@@ -12993,18 +12995,18 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9B20742-2F64-BB4D-931D-0ED7AB74219D}">
   <dimension ref="A1:AM11"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="158.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.58203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.08203125" customWidth="1"/>
+    <col min="1" max="1" width="158.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.09765625" customWidth="1"/>
     <col min="7" max="7" width="24.5" customWidth="1"/>
-    <col min="11" max="11" width="8.75" customWidth="1"/>
-    <col min="12" max="12" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.69921875" customWidth="1"/>
+    <col min="12" max="12" width="47.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="11" customFormat="1" ht="16" thickBot="1">
+    <row r="1" spans="1:39" s="11" customFormat="1" ht="16.2" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>118</v>
       </c>
@@ -13123,7 +13125,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="17" thickBot="1">
+    <row r="2" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A2" s="66" t="s">
         <v>338</v>
       </c>
@@ -13278,7 +13280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="17" thickBot="1">
+    <row r="3" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A3" s="66" t="s">
         <v>339</v>
       </c>
@@ -13433,7 +13435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="17" thickBot="1">
+    <row r="4" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A4" s="66" t="s">
         <v>340</v>
       </c>
@@ -13588,7 +13590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="17" thickBot="1">
+    <row r="5" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A5" s="66" t="s">
         <v>341</v>
       </c>
@@ -13743,7 +13745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="17" thickBot="1">
+    <row r="6" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A6" s="66" t="s">
         <v>342</v>
       </c>
@@ -13898,7 +13900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="17" thickBot="1">
+    <row r="7" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A7" s="66" t="s">
         <v>343</v>
       </c>
@@ -14053,7 +14055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="17" thickBot="1">
+    <row r="8" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A8" s="66" t="s">
         <v>344</v>
       </c>
@@ -14208,7 +14210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:39" ht="17" thickBot="1">
+    <row r="9" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A9" s="66" t="s">
         <v>345</v>
       </c>
@@ -14363,7 +14365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="17" thickBot="1">
+    <row r="10" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A10" s="66" t="s">
         <v>346</v>
       </c>
@@ -14518,7 +14520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="17" thickBot="1">
+    <row r="11" spans="1:39" ht="17.399999999999999" thickBot="1">
       <c r="A11" s="66" t="s">
         <v>347</v>
       </c>
@@ -14685,15 +14687,15 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22440E3A-6E10-F44C-A8EB-A92A916ABD32}">
   <dimension ref="A1:AL13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="128.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="11" customFormat="1" ht="16" thickBot="1">
+    <row r="1" spans="1:38" s="11" customFormat="1" ht="16.2" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>118</v>
       </c>
@@ -14809,7 +14811,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="17" thickBot="1">
+    <row r="2" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A2" s="67" t="s">
         <v>348</v>
       </c>
@@ -14960,7 +14962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="17" thickBot="1">
+    <row r="3" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A3" s="67" t="s">
         <v>349</v>
       </c>
@@ -15111,7 +15113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="17" thickBot="1">
+    <row r="4" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A4" s="67" t="s">
         <v>350</v>
       </c>
@@ -15262,7 +15264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="17" thickBot="1">
+    <row r="5" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A5" s="67" t="s">
         <v>351</v>
       </c>
@@ -15413,7 +15415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="17" thickBot="1">
+    <row r="6" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A6" s="67" t="s">
         <v>352</v>
       </c>
@@ -15564,7 +15566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="17" thickBot="1">
+    <row r="7" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A7" s="67" t="s">
         <v>353</v>
       </c>
@@ -15715,7 +15717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="17" thickBot="1">
+    <row r="8" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A8" s="67" t="s">
         <v>354</v>
       </c>
@@ -15866,7 +15868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="17" thickBot="1">
+    <row r="9" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A9" s="67" t="s">
         <v>355</v>
       </c>
@@ -16017,7 +16019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="17" thickBot="1">
+    <row r="10" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A10" s="67" t="s">
         <v>356</v>
       </c>
@@ -16168,7 +16170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="17" thickBot="1">
+    <row r="11" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A11" s="67" t="s">
         <v>357</v>
       </c>
@@ -16319,7 +16321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="17" thickBot="1">
+    <row r="12" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A12" s="67" t="s">
         <v>358</v>
       </c>
@@ -16470,7 +16472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="17" thickBot="1">
+    <row r="13" spans="1:38" ht="17.399999999999999" thickBot="1">
       <c r="A13" s="67" t="s">
         <v>359</v>
       </c>
@@ -16632,14 +16634,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA53CA9E-5475-8E48-80D6-77CE99F7CA3D}">
   <dimension ref="A1:AM5"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="114.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="114.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="11" customFormat="1" ht="16" thickBot="1">
+    <row r="1" spans="1:39" s="11" customFormat="1" ht="16.2" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>118</v>
       </c>
@@ -16758,7 +16760,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="16" thickBot="1">
+    <row r="2" spans="1:39" ht="16.2" thickBot="1">
       <c r="A2" s="68" t="s">
         <v>360</v>
       </c>
@@ -16913,7 +16915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="16" thickBot="1">
+    <row r="3" spans="1:39" ht="16.2" thickBot="1">
       <c r="A3" s="68" t="s">
         <v>361</v>
       </c>
@@ -17068,7 +17070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="16" thickBot="1">
+    <row r="4" spans="1:39" ht="16.2" thickBot="1">
       <c r="A4" s="68" t="s">
         <v>400</v>
       </c>
@@ -17223,7 +17225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="16" thickBot="1">
+    <row r="5" spans="1:39" ht="16.2" thickBot="1">
       <c r="A5" s="68" t="s">
         <v>401</v>
       </c>
@@ -17393,15 +17395,15 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35458118-D48A-D94F-8815-70903938F945}">
   <dimension ref="A1:AM7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="105" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="11" customFormat="1" ht="16" thickBot="1">
+    <row r="1" spans="1:39" s="11" customFormat="1" ht="16.2" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>118</v>
       </c>
@@ -17520,7 +17522,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="16" thickBot="1">
+    <row r="2" spans="1:39" ht="16.2" thickBot="1">
       <c r="A2" s="71" t="s">
         <v>403</v>
       </c>
@@ -17558,9 +17560,8 @@
         <f t="array" ref="J2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(J$1,dataRowRange,ActualDataRange))</f>
         <v>ATL</v>
       </c>
-      <c r="K2" s="31" t="str" cm="1">
-        <f t="array" ref="K2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(K$1,dataRowRange,ActualDataRange))</f>
-        <v>MSP</v>
+      <c r="K2" s="75" t="s">
+        <v>143</v>
       </c>
       <c r="L2" s="31" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
@@ -17675,7 +17676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="16" thickBot="1">
+    <row r="3" spans="1:39" ht="16.2" thickBot="1">
       <c r="A3" s="72" t="s">
         <v>404</v>
       </c>
@@ -17830,7 +17831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="16" thickBot="1">
+    <row r="4" spans="1:39" ht="16.2" thickBot="1">
       <c r="A4" s="72" t="s">
         <v>405</v>
       </c>
@@ -17985,7 +17986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="16" thickBot="1">
+    <row r="5" spans="1:39" ht="16.2" thickBot="1">
       <c r="A5" s="72" t="s">
         <v>406</v>
       </c>
@@ -18140,7 +18141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="16" thickBot="1">
+    <row r="6" spans="1:39" ht="16.2" thickBot="1">
       <c r="A6" s="72" t="s">
         <v>407</v>
       </c>
@@ -18295,7 +18296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="16" thickBot="1">
+    <row r="7" spans="1:39" ht="16.2" thickBot="1">
       <c r="A7" s="72" t="s">
         <v>408</v>
       </c>
@@ -18462,13 +18463,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8DD980-905D-FC4A-81AD-0000D690C0FF}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="47.58203125" style="11" customWidth="1"/>
-    <col min="2" max="3" width="16.58203125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="47.59765625" style="11" customWidth="1"/>
+    <col min="2" max="3" width="16.59765625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" style="11" customWidth="1"/>
     <col min="5" max="5" width="31" style="11" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="11"/>
+    <col min="6" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -18488,7 +18489,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="32.15" customHeight="1">
+    <row r="2" spans="1:5" ht="32.1" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>139</v>
       </c>
@@ -18506,7 +18507,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16">
+    <row r="3" spans="1:5">
       <c r="A3" s="11" t="s">
         <v>138</v>
       </c>
@@ -18524,7 +18525,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16">
+    <row r="4" spans="1:5">
       <c r="A4" s="11" t="s">
         <v>167</v>
       </c>
@@ -18542,7 +18543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16">
+    <row r="5" spans="1:5">
       <c r="A5" s="11" t="s">
         <v>168</v>
       </c>
@@ -18560,7 +18561,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16">
+    <row r="6" spans="1:5">
       <c r="A6" s="11" t="s">
         <v>169</v>
       </c>
@@ -18578,7 +18579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16">
+    <row r="7" spans="1:5">
       <c r="A7" s="11" t="s">
         <v>170</v>
       </c>
@@ -18596,7 +18597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16">
+    <row r="8" spans="1:5">
       <c r="A8" s="11" t="s">
         <v>199</v>
       </c>
@@ -18785,46 +18786,46 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DAEE888-1773-9E47-9558-1F0A440779BF}">
   <dimension ref="A1:AL129"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="104.1640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.08203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="104.19921875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.296875" style="2" customWidth="1"/>
     <col min="4" max="4" width="25.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.83203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.296875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.796875" style="2" customWidth="1"/>
     <col min="8" max="8" width="14" style="2" customWidth="1"/>
     <col min="9" max="9" width="18.5" style="2" customWidth="1"/>
     <col min="10" max="10" width="52" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.796875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.5" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.5" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.296875" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="37.08203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="21.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="37.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="21.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.09765625" style="2" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="28" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.83203125" style="2"/>
-    <col min="26" max="26" width="34.58203125" style="2" customWidth="1"/>
-    <col min="27" max="27" width="22.08203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="22.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="8.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.796875" style="2"/>
+    <col min="26" max="26" width="34.59765625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="22.09765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="8.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.796875" style="2" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="7.5" style="2" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.33203125" style="2" customWidth="1"/>
-    <col min="37" max="37" width="4.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.58203125" style="2" customWidth="1"/>
-    <col min="39" max="16384" width="10.83203125" style="2"/>
+    <col min="35" max="35" width="14.296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.296875" style="2" customWidth="1"/>
+    <col min="37" max="37" width="4.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.59765625" style="2" customWidth="1"/>
+    <col min="39" max="16384" width="10.796875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -33233,7 +33234,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL129" xr:uid="{1DAEE888-1773-9E47-9558-1F0A440779BF}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{A27DD8EB-70E3-9343-A2F0-4EC1F414F378}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{B7F22B40-D1E3-41A2-B580-43255BDF4D3A}"/>
@@ -33373,44 +33374,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F99C04-ED4A-B140-B723-3FB745556183}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AO7"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="89.5" style="38" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="38" customWidth="1"/>
-    <col min="4" max="4" width="13.08203125" style="38" customWidth="1"/>
-    <col min="5" max="5" width="39.08203125" style="38" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.33203125" style="38" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" style="38" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="33.58203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.296875" style="38" customWidth="1"/>
+    <col min="4" max="4" width="13.09765625" style="38" customWidth="1"/>
+    <col min="5" max="5" width="39.09765625" style="38" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.796875" style="38" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.796875" style="38" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.296875" style="38" customWidth="1"/>
+    <col min="11" max="11" width="15.296875" style="38" customWidth="1"/>
+    <col min="12" max="12" width="18.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.59765625" style="38" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19" style="38" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37.08203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.58203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.08203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.09765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.59765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.09765625" style="38" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="28" style="38" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="19" style="38" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="32.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="37.08203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.58203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.58203125" style="38" customWidth="1"/>
-    <col min="25" max="25" width="27.33203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="32.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="37.09765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.59765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="26.59765625" style="38" customWidth="1"/>
+    <col min="25" max="25" width="27.296875" style="38" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13" style="38" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="22.08203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="29" max="35" width="10.83203125" style="38"/>
+    <col min="27" max="27" width="14.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.09765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="29" max="35" width="10.796875" style="38"/>
     <col min="36" max="36" width="14.5" style="38" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="14.5" style="38" customWidth="1"/>
-    <col min="38" max="38" width="10.83203125" style="38"/>
-    <col min="39" max="39" width="25.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="37.08203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="21.58203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="10.83203125" style="38"/>
+    <col min="38" max="38" width="10.796875" style="38"/>
+    <col min="39" max="39" width="25.296875" style="38" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="37.09765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="21.59765625" style="38" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="10.796875" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41">
@@ -33538,7 +33539,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="16">
+    <row r="2" spans="1:41">
       <c r="A2" s="39" t="s">
         <v>212</v>
       </c>
@@ -33701,7 +33702,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:41" ht="16">
+    <row r="3" spans="1:41">
       <c r="A3" s="39" t="s">
         <v>213</v>
       </c>
@@ -33864,7 +33865,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="16">
+    <row r="4" spans="1:41">
       <c r="A4" s="39" t="s">
         <v>214</v>
       </c>
@@ -34028,7 +34029,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="16">
+    <row r="5" spans="1:41">
       <c r="A5" s="39" t="s">
         <v>217</v>
       </c>
@@ -34192,7 +34193,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="16">
+    <row r="6" spans="1:41">
       <c r="A6" s="39" t="s">
         <v>218</v>
       </c>
@@ -34356,7 +34357,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="16">
+    <row r="7" spans="1:41">
       <c r="A7" s="39" t="s">
         <v>219</v>
       </c>
@@ -34521,7 +34522,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" location="AdvBkngSTD!A1" display="AdvBkngSTD" xr:uid="{9836EF3A-0C81-384A-B28E-38769E19AD72}"/>
     <hyperlink ref="A1" location="TestCaseConfig!A1" display="TestCases" xr:uid="{B061C974-A2F8-7C4C-A5EC-974E6D31B128}"/>
@@ -34536,40 +34537,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C996C58-3C8B-D941-9CF9-2A0431D4505C}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AL11"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="131.58203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="131.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="23.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" style="11" customWidth="1"/>
     <col min="5" max="5" width="25.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.796875" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="29" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="38.58203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.296875" style="28" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="10.83203125" style="11"/>
-    <col min="16" max="16" width="21.58203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.08203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="10.796875" style="11"/>
+    <col min="16" max="16" width="21.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="28" style="11" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" style="11" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.83203125" style="11"/>
-    <col min="21" max="21" width="22.08203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="22.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.58203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.83203125" style="11"/>
-    <col min="26" max="26" width="14.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="38.58203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="22.08203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.58203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="10.83203125" style="11"/>
-    <col min="36" max="36" width="14.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.33203125" style="11" customWidth="1"/>
-    <col min="38" max="16384" width="10.83203125" style="11"/>
+    <col min="20" max="20" width="10.796875" style="11"/>
+    <col min="21" max="21" width="22.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.796875" style="11"/>
+    <col min="26" max="26" width="14.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="38.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="22.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="22.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="10.796875" style="11"/>
+    <col min="36" max="36" width="14.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.296875" style="11" customWidth="1"/>
+    <col min="38" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -34688,7 +34689,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="16.5">
+    <row r="2" spans="1:38" ht="16.8">
       <c r="A2" s="33" t="s">
         <v>231</v>
       </c>
@@ -34839,7 +34840,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="16.5">
+    <row r="3" spans="1:38" ht="16.8">
       <c r="A3" s="33" t="s">
         <v>232</v>
       </c>
@@ -34990,7 +34991,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="16.5">
+    <row r="4" spans="1:38" ht="16.8">
       <c r="A4" s="33" t="s">
         <v>233</v>
       </c>
@@ -35141,7 +35142,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="16.5">
+    <row r="5" spans="1:38" ht="16.8">
       <c r="A5" s="33" t="s">
         <v>234</v>
       </c>
@@ -35292,7 +35293,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="16.5">
+    <row r="6" spans="1:38" ht="16.8">
       <c r="A6" s="33" t="s">
         <v>235</v>
       </c>
@@ -35443,7 +35444,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="16.5">
+    <row r="7" spans="1:38" ht="16.8">
       <c r="A7" s="33" t="s">
         <v>236</v>
       </c>
@@ -35594,7 +35595,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="16.5">
+    <row r="8" spans="1:38" ht="16.8">
       <c r="A8" s="33" t="s">
         <v>237</v>
       </c>
@@ -35745,7 +35746,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="16.5">
+    <row r="9" spans="1:38" ht="16.8">
       <c r="A9" s="33" t="s">
         <v>238</v>
       </c>
@@ -35896,7 +35897,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="16.5">
+    <row r="10" spans="1:38" ht="16.8">
       <c r="A10" s="33" t="s">
         <v>239</v>
       </c>
@@ -36047,7 +36048,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="16.5">
+    <row r="11" spans="1:38" ht="16.8">
       <c r="A11" s="33" t="s">
         <v>240</v>
       </c>
@@ -36213,17 +36214,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E70DB7-4DD6-624F-9EA1-30DDDFA58DD7}">
   <dimension ref="A1:AL11"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="145.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="145.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" style="11" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="10.83203125" style="11"/>
-    <col min="11" max="11" width="49.08203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="11"/>
+    <col min="3" max="3" width="23.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.296875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="23.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="10.796875" style="11"/>
+    <col min="11" max="11" width="49.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.296875" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -36342,7 +36343,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="16.5">
+    <row r="2" spans="1:38" ht="16.8">
       <c r="A2" s="33" t="s">
         <v>241</v>
       </c>
@@ -36493,7 +36494,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="16.5">
+    <row r="3" spans="1:38" ht="16.8">
       <c r="A3" s="33" t="s">
         <v>242</v>
       </c>
@@ -36644,7 +36645,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="16.5">
+    <row r="4" spans="1:38" ht="16.8">
       <c r="A4" s="33" t="s">
         <v>243</v>
       </c>
@@ -36795,7 +36796,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="16.5">
+    <row r="5" spans="1:38" ht="16.8">
       <c r="A5" s="33" t="s">
         <v>244</v>
       </c>
@@ -36946,7 +36947,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="16.5">
+    <row r="6" spans="1:38" ht="16.8">
       <c r="A6" s="33" t="s">
         <v>245</v>
       </c>
@@ -37097,7 +37098,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="16.5">
+    <row r="7" spans="1:38" ht="16.8">
       <c r="A7" s="33" t="s">
         <v>246</v>
       </c>
@@ -37248,7 +37249,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="16.5">
+    <row r="8" spans="1:38" ht="16.8">
       <c r="A8" s="33" t="s">
         <v>247</v>
       </c>
@@ -37399,7 +37400,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="16.5">
+    <row r="9" spans="1:38" ht="16.8">
       <c r="A9" s="33" t="s">
         <v>248</v>
       </c>
@@ -37550,7 +37551,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="16.5">
+    <row r="10" spans="1:38" ht="16.8">
       <c r="A10" s="33" t="s">
         <v>249</v>
       </c>
@@ -37701,7 +37702,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="16.5">
+    <row r="11" spans="1:38" ht="16.8">
       <c r="A11" s="33" t="s">
         <v>250</v>
       </c>
@@ -37866,16 +37867,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E262B8C-B72A-DD49-A994-304B68688876}">
   <dimension ref="A1:AL13"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="131.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.83203125" style="11"/>
+    <col min="2" max="3" width="10.796875" style="11"/>
     <col min="4" max="4" width="13" style="11" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="10.83203125" style="11"/>
-    <col min="11" max="11" width="47.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="11"/>
+    <col min="5" max="5" width="23.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="10.796875" style="11"/>
+    <col min="11" max="11" width="47.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.296875" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -37994,7 +37995,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="16.5">
+    <row r="2" spans="1:38" ht="16.8">
       <c r="A2" s="32" t="s">
         <v>251</v>
       </c>
@@ -38145,7 +38146,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="16.5">
+    <row r="3" spans="1:38" ht="16.8">
       <c r="A3" s="32" t="s">
         <v>252</v>
       </c>
@@ -38296,7 +38297,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="16.5">
+    <row r="4" spans="1:38" ht="16.8">
       <c r="A4" s="32" t="s">
         <v>253</v>
       </c>
@@ -38447,7 +38448,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="16.5">
+    <row r="5" spans="1:38" ht="16.8">
       <c r="A5" s="32" t="s">
         <v>254</v>
       </c>
@@ -38598,7 +38599,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="16.5">
+    <row r="6" spans="1:38" ht="16.8">
       <c r="A6" s="32" t="s">
         <v>255</v>
       </c>
@@ -38749,7 +38750,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="16.5">
+    <row r="7" spans="1:38" ht="16.8">
       <c r="A7" s="32" t="s">
         <v>256</v>
       </c>
@@ -38900,7 +38901,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="16.5">
+    <row r="8" spans="1:38" ht="16.8">
       <c r="A8" s="32" t="s">
         <v>257</v>
       </c>
@@ -39051,7 +39052,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="16.5">
+    <row r="9" spans="1:38" ht="16.8">
       <c r="A9" s="32" t="s">
         <v>258</v>
       </c>
@@ -39202,7 +39203,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="16.5">
+    <row r="10" spans="1:38" ht="16.8">
       <c r="A10" s="32" t="s">
         <v>259</v>
       </c>
@@ -39353,7 +39354,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="16.5">
+    <row r="11" spans="1:38" ht="16.8">
       <c r="A11" s="32" t="s">
         <v>260</v>
       </c>
@@ -39504,7 +39505,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="16.5">
+    <row r="12" spans="1:38" ht="16.8">
       <c r="A12" s="32" t="s">
         <v>261</v>
       </c>
@@ -39655,7 +39656,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="16.5">
+    <row r="13" spans="1:38" ht="16.8">
       <c r="A13" s="32" t="s">
         <v>262</v>
       </c>
@@ -39820,17 +39821,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7990930-FE48-954E-9FFC-70384FD7E025}">
   <dimension ref="A1:AL5"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="102.5" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.58203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="10.83203125" style="11"/>
+    <col min="3" max="3" width="23.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="10.796875" style="11"/>
     <col min="11" max="11" width="24.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="11"/>
+    <col min="12" max="12" width="18.296875" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -39949,7 +39950,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="16.5">
+    <row r="2" spans="1:38" ht="16.8">
       <c r="A2" s="33" t="s">
         <v>263</v>
       </c>
@@ -40100,7 +40101,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="16.5">
+    <row r="3" spans="1:38" ht="16.8">
       <c r="A3" s="33" t="s">
         <v>264</v>
       </c>
@@ -40251,7 +40252,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="16.5">
+    <row r="4" spans="1:38" ht="16.8">
       <c r="A4" s="33" t="s">
         <v>265</v>
       </c>
@@ -40402,7 +40403,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="16.5">
+    <row r="5" spans="1:38" ht="16.8">
       <c r="A5" s="33" t="s">
         <v>266</v>
       </c>
@@ -40566,19 +40567,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E94645-B80F-0D4E-B109-C05D67A154E2}">
   <dimension ref="A1:AL7"/>
-  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="106.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="106.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="10.83203125" style="11"/>
-    <col min="11" max="11" width="15.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="10.796875" style="11"/>
+    <col min="11" max="11" width="15.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.296875" style="28" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.5" style="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.83203125" style="11"/>
+    <col min="15" max="16384" width="10.796875" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -40697,7 +40698,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="16.5">
+    <row r="2" spans="1:38" ht="16.8">
       <c r="A2" s="32" t="s">
         <v>267</v>
       </c>
@@ -40848,7 +40849,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="16.5">
+    <row r="3" spans="1:38" ht="16.8">
       <c r="A3" s="32" t="s">
         <v>268</v>
       </c>
@@ -40999,7 +41000,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="16.5">
+    <row r="4" spans="1:38" ht="16.8">
       <c r="A4" s="32" t="s">
         <v>269</v>
       </c>
@@ -41150,7 +41151,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="16.5">
+    <row r="5" spans="1:38" ht="16.8">
       <c r="A5" s="32" t="s">
         <v>270</v>
       </c>
@@ -41301,7 +41302,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="16.5">
+    <row r="6" spans="1:38" ht="16.8">
       <c r="A6" s="32" t="s">
         <v>271</v>
       </c>
@@ -41452,7 +41453,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="16.5">
+    <row r="7" spans="1:38" ht="16.8">
       <c r="A7" s="32" t="s">
         <v>272</v>
       </c>
@@ -41745,18 +41746,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41778,14 +41779,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD641CF5-135D-42FC-A55D-82791A85B476}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C30B22D-1747-44FE-B15C-A00BE24DA1E1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -41799,4 +41792,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD641CF5-135D-42FC-A55D-82791A85B476}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
+++ b/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p57448\Desktop\Drafts\My Repo Excelbackup\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p57448\Desktop\Cargo_B\Cargo\CargoUIAutomationNew\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A29A29C6-B167-4455-BD00-2A3DF67FD2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88D73FF-7ED1-4686-9DBF-040B049153AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="3" xr2:uid="{1AB005B2-AFEC-3B46-93EF-50FA3BE3C5FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{1AB005B2-AFEC-3B46-93EF-50FA3BE3C5FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="14" r:id="rId1"/>
@@ -1099,27 +1099,6 @@
     <t>createAndConfirmGuidedBookingValuables_SAFE_Valuelessthan25000USD_International</t>
   </si>
   <si>
-    <t>CARE</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_Domestic</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_Domestic</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_Domestic</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_International</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_International</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_International</t>
-  </si>
-  <si>
     <t>createAndConfirmAdvanceBookingGeneral_Cargo_STANDARD_Loose_Domestic</t>
   </si>
   <si>
@@ -1304,6 +1283,27 @@
   </si>
   <si>
     <t>createAndConfirmAdvanceBookingLiveAnimals_LIVE_HatchingEggs_International</t>
+  </si>
+  <si>
+    <t>Cares</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_Domestic</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_Domestic</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_Domestic</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_International</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_International</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_International</t>
   </si>
 </sst>
 </file>
@@ -2367,7 +2367,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>210</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>210</v>
@@ -2669,7 +2669,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>210</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>210</v>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>210</v>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>210</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>210</v>
@@ -3424,7 +3424,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>210</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>210</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>210</v>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="12" spans="1:38" ht="17" thickBot="1">
       <c r="A12" s="75" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>210</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="13" spans="1:38" ht="17" thickBot="1">
       <c r="A13" s="75" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>210</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="14" spans="1:38" ht="17" thickBot="1">
       <c r="A14" s="75" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>210</v>
@@ -4330,7 +4330,7 @@
     </row>
     <row r="15" spans="1:38" ht="17" thickBot="1">
       <c r="A15" s="75" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B15" s="32" t="s">
         <v>210</v>
@@ -17519,13 +17519,13 @@
     </row>
     <row r="2" spans="1:39" ht="16" thickBot="1">
       <c r="A2" s="70" t="s">
-        <v>340</v>
+        <v>402</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>311</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D2" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="E2" s="31" t="str" cm="1">
         <f t="array" ref="E2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F2" s="31" t="str" cm="1">
         <f t="array" ref="F2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -17674,13 +17674,13 @@
     </row>
     <row r="3" spans="1:39" ht="16" thickBot="1">
       <c r="A3" s="71" t="s">
-        <v>341</v>
+        <v>403</v>
       </c>
       <c r="B3" s="42" t="s">
         <v>311</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D3" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="E3" s="31" t="str" cm="1">
         <f t="array" ref="E3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F3" s="31" t="str" cm="1">
         <f t="array" ref="F3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -17829,13 +17829,13 @@
     </row>
     <row r="4" spans="1:39" ht="16" thickBot="1">
       <c r="A4" s="71" t="s">
-        <v>342</v>
+        <v>404</v>
       </c>
       <c r="B4" s="42" t="s">
         <v>311</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D4" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="E4" s="31" t="str" cm="1">
         <f t="array" ref="E4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F4" s="31" t="str" cm="1">
         <f t="array" ref="F4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -17984,13 +17984,13 @@
     </row>
     <row r="5" spans="1:39" ht="16" thickBot="1">
       <c r="A5" s="71" t="s">
-        <v>343</v>
+        <v>405</v>
       </c>
       <c r="B5" s="42" t="s">
         <v>311</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D5" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17998,7 +17998,7 @@
       </c>
       <c r="E5" s="31" t="str" cm="1">
         <f t="array" ref="E5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F5" s="31" t="str" cm="1">
         <f t="array" ref="F5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -18139,13 +18139,13 @@
     </row>
     <row r="6" spans="1:39" ht="16" thickBot="1">
       <c r="A6" s="71" t="s">
-        <v>344</v>
+        <v>406</v>
       </c>
       <c r="B6" s="42" t="s">
         <v>311</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D6" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="E6" s="31" t="str" cm="1">
         <f t="array" ref="E6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F6" s="31" t="str" cm="1">
         <f t="array" ref="F6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -18294,13 +18294,13 @@
     </row>
     <row r="7" spans="1:39" ht="16" thickBot="1">
       <c r="A7" s="71" t="s">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="B7" s="42" t="s">
         <v>311</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D7" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -18308,7 +18308,7 @@
       </c>
       <c r="E7" s="31" t="str" cm="1">
         <f t="array" ref="E7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F7" s="31" t="str" cm="1">
         <f t="array" ref="F7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -32565,13 +32565,13 @@
     <row r="124" spans="1:36" s="61" customFormat="1">
       <c r="A124" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_Domestic</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_Domestic</v>
       </c>
       <c r="B124" s="61" t="s">
         <v>311</v>
       </c>
       <c r="C124" s="61" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D124" s="46" t="s">
         <v>125</v>
@@ -32676,13 +32676,13 @@
     <row r="125" spans="1:36" s="61" customFormat="1">
       <c r="A125" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_Domestic</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_Domestic</v>
       </c>
       <c r="B125" s="61" t="s">
         <v>311</v>
       </c>
       <c r="C125" s="61" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D125" s="46" t="s">
         <v>125</v>
@@ -32787,13 +32787,13 @@
     <row r="126" spans="1:36" s="61" customFormat="1">
       <c r="A126" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_Domestic</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_Domestic</v>
       </c>
       <c r="B126" s="61" t="s">
         <v>311</v>
       </c>
       <c r="C126" s="61" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D126" s="46" t="s">
         <v>125</v>
@@ -32898,13 +32898,13 @@
     <row r="127" spans="1:36" s="61" customFormat="1">
       <c r="A127" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_International</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_International</v>
       </c>
       <c r="B127" s="61" t="s">
         <v>311</v>
       </c>
       <c r="C127" s="61" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D127" s="46" t="s">
         <v>125</v>
@@ -33009,13 +33009,13 @@
     <row r="128" spans="1:36" s="61" customFormat="1">
       <c r="A128" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_International</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_International</v>
       </c>
       <c r="B128" s="61" t="s">
         <v>311</v>
       </c>
       <c r="C128" s="61" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D128" s="46" t="s">
         <v>125</v>
@@ -33120,13 +33120,13 @@
     <row r="129" spans="1:36" s="61" customFormat="1">
       <c r="A129" s="61" t="str">
         <f t="shared" ref="A129" si="2">_xlfn.CONCAT("createAndConfirmGuidedBooking",SUBSTITUTE(B129," ","_"),"_",SUBSTITUTE(C129," ","_"),"_",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J129," ",""),"-",""),"/",""),"–",""),"+",""),"°",""),",",""),"_",SUBSTITUTE(AJ129," ","_"))</f>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_International</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_International</v>
       </c>
       <c r="B129" s="61" t="s">
         <v>311</v>
       </c>
       <c r="C129" s="61" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="D129" s="46" t="s">
         <v>125</v>
@@ -33537,7 +33537,7 @@
     </row>
     <row r="2" spans="1:41" ht="16.5" thickBot="1">
       <c r="A2" s="74" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B2" s="38" t="str" cm="1">
         <f t="array" ref="B2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -33700,7 +33700,7 @@
     </row>
     <row r="3" spans="1:41" ht="16.5" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B3" s="38" t="str" cm="1">
         <f t="array" ref="B3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -33863,7 +33863,7 @@
     </row>
     <row r="4" spans="1:41" ht="16.5" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B4" s="38" t="str" cm="1">
         <f t="array" ref="B4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -34027,7 +34027,7 @@
     </row>
     <row r="5" spans="1:41" ht="16.5" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B5" s="38" t="str" cm="1">
         <f t="array" ref="B5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -34191,7 +34191,7 @@
     </row>
     <row r="6" spans="1:41" ht="16.5" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B6" s="38" t="str" cm="1">
         <f t="array" ref="B6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -34355,7 +34355,7 @@
     </row>
     <row r="7" spans="1:41" ht="16.5" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B7" s="38" t="str" cm="1">
         <f t="array" ref="B7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -34687,7 +34687,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>47</v>
@@ -34838,7 +34838,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>47</v>
@@ -34989,7 +34989,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>47</v>
@@ -35140,7 +35140,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>47</v>
@@ -35291,7 +35291,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>47</v>
@@ -35442,7 +35442,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>47</v>
@@ -35593,7 +35593,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>47</v>
@@ -35744,7 +35744,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>47</v>
@@ -35895,7 +35895,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>47</v>
@@ -36046,7 +36046,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>47</v>
@@ -36341,7 +36341,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>58</v>
@@ -36492,7 +36492,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>58</v>
@@ -36643,7 +36643,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>58</v>
@@ -36794,7 +36794,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>58</v>
@@ -36945,7 +36945,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>58</v>
@@ -37096,7 +37096,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>58</v>
@@ -37247,7 +37247,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>58</v>
@@ -37398,7 +37398,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>58</v>
@@ -37549,7 +37549,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>58</v>
@@ -37700,7 +37700,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>58</v>
@@ -37993,7 +37993,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>44</v>
@@ -38144,7 +38144,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>44</v>
@@ -38295,7 +38295,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>44</v>
@@ -38446,7 +38446,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>44</v>
@@ -38597,7 +38597,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>44</v>
@@ -38748,7 +38748,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>44</v>
@@ -38899,7 +38899,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>44</v>
@@ -39050,7 +39050,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>44</v>
@@ -39201,7 +39201,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>44</v>
@@ -39352,7 +39352,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>44</v>
@@ -39503,7 +39503,7 @@
     </row>
     <row r="12" spans="1:38" ht="17" thickBot="1">
       <c r="A12" s="75" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>44</v>
@@ -39654,7 +39654,7 @@
     </row>
     <row r="13" spans="1:38" ht="17" thickBot="1">
       <c r="A13" s="75" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>44</v>
@@ -39948,7 +39948,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>87</v>
@@ -40099,7 +40099,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>87</v>
@@ -40250,7 +40250,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>87</v>
@@ -40401,7 +40401,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>87</v>
@@ -40696,7 +40696,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>89</v>
@@ -40847,7 +40847,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>89</v>
@@ -40998,7 +40998,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>89</v>
@@ -41149,7 +41149,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>89</v>
@@ -41300,7 +41300,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>89</v>
@@ -41451,7 +41451,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>89</v>
@@ -41610,6 +41610,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DFBCF867C5410147BDDAF2BCA37BA4E7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e24a40d5ebdbb3b92553f235188d50f6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2981db02-ca81-468a-9abd-70e82312b342" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db49c26ce236f576151feb411775a695" ns2:_="">
     <xsd:import namespace="2981db02-ca81-468a-9abd-70e82312b342"/>
@@ -41741,22 +41756,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C30B22D-1747-44FE-B15C-A00BE24DA1E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="2981db02-ca81-468a-9abd-70e82312b342"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD641CF5-135D-42FC-A55D-82791A85B476}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED3BB4E-382D-479A-B77C-6CB5E1CFD30D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41772,28 +41796,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD641CF5-135D-42FC-A55D-82791A85B476}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C30B22D-1747-44FE-B15C-A00BE24DA1E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="2981db02-ca81-468a-9abd-70e82312b342"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
+++ b/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p57448\Desktop\Cargo_B\Cargo\CargoUIAutomationNew\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88D73FF-7ED1-4686-9DBF-040B049153AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B728B9E9-3CDF-4A88-969B-5C6C1DFDCA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{1AB005B2-AFEC-3B46-93EF-50FA3BE3C5FF}"/>
   </bookViews>
@@ -17724,7 +17724,7 @@
       </c>
       <c r="N3" s="31" cm="1">
         <f t="array" ref="N3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(N$1,dataRowRange,ActualDataRange))</f>
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="O3" s="31" t="str" cm="1">
         <f t="array" ref="O3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(O$1,dataRowRange,ActualDataRange))</f>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="N6" s="31" cm="1">
         <f t="array" ref="N6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(N$1,dataRowRange,ActualDataRange))</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O6" s="31" t="str" cm="1">
         <f t="array" ref="O6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(O$1,dataRowRange,ActualDataRange))</f>
@@ -32709,7 +32709,7 @@
         <v>308</v>
       </c>
       <c r="L125" s="61">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="M125" s="61" t="s">
         <v>145</v>
@@ -33042,7 +33042,7 @@
         <v>308</v>
       </c>
       <c r="L128" s="61">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M128" s="61" t="s">
         <v>198</v>
@@ -41610,21 +41610,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DFBCF867C5410147BDDAF2BCA37BA4E7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e24a40d5ebdbb3b92553f235188d50f6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2981db02-ca81-468a-9abd-70e82312b342" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db49c26ce236f576151feb411775a695" ns2:_="">
     <xsd:import namespace="2981db02-ca81-468a-9abd-70e82312b342"/>
@@ -41756,31 +41741,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C30B22D-1747-44FE-B15C-A00BE24DA1E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="2981db02-ca81-468a-9abd-70e82312b342"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD641CF5-135D-42FC-A55D-82791A85B476}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED3BB4E-382D-479A-B77C-6CB5E1CFD30D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41796,4 +41772,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD641CF5-135D-42FC-A55D-82791A85B476}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C30B22D-1747-44FE-B15C-A00BE24DA1E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="2981db02-ca81-468a-9abd-70e82312b342"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
+++ b/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p57448\Desktop\Cargo_B\Cargo\CargoUIAutomationNew\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B728B9E9-3CDF-4A88-969B-5C6C1DFDCA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130465E4-222D-4F23-AF9F-5549C932BCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{1AB005B2-AFEC-3B46-93EF-50FA3BE3C5FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="2" xr2:uid="{1AB005B2-AFEC-3B46-93EF-50FA3BE3C5FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="14" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5270" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5270" uniqueCount="409">
   <si>
     <t>LoginCredentials</t>
   </si>
@@ -673,9 +673,6 @@
     <t>ShipmentDescription</t>
   </si>
   <si>
-    <t>Test</t>
-  </si>
-  <si>
     <t>KG</t>
   </si>
   <si>
@@ -1099,6 +1096,27 @@
     <t>createAndConfirmGuidedBookingValuables_SAFE_Valuelessthan25000USD_International</t>
   </si>
   <si>
+    <t>CARE</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_Domestic</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_Domestic</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_Domestic</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_International</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_International</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_International</t>
+  </si>
+  <si>
     <t>createAndConfirmAdvanceBookingGeneral_Cargo_STANDARD_Loose_Domestic</t>
   </si>
   <si>
@@ -1285,25 +1303,10 @@
     <t>createAndConfirmAdvanceBookingLiveAnimals_LIVE_HatchingEggs_International</t>
   </si>
   <si>
-    <t>Cares</t>
+    <t>Test General Cargo</t>
   </si>
   <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_Domestic</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_Domestic</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_Domestic</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_International</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_International</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_International</t>
+    <t>Test Human Remains</t>
   </si>
 </sst>
 </file>
@@ -2281,7 +2284,7 @@
         <v>141</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L1" s="27" t="s">
         <v>196</v>
@@ -2359,7 +2362,7 @@
         <v>102</v>
       </c>
       <c r="AK1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL1" s="20" t="s">
         <v>73</v>
@@ -2367,13 +2370,13 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D2" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -2409,7 +2412,7 @@
       </c>
       <c r="L2" s="31" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M2" s="31" cm="1">
         <f t="array" ref="M2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -2518,13 +2521,13 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D3" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -2560,7 +2563,7 @@
       </c>
       <c r="L3" s="31" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M3" s="31" cm="1">
         <f t="array" ref="M3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -2669,13 +2672,13 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D4" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -2711,7 +2714,7 @@
       </c>
       <c r="L4" s="31" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M4" s="31" cm="1">
         <f t="array" ref="M4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -2820,13 +2823,13 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D5" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -2862,7 +2865,7 @@
       </c>
       <c r="L5" s="31" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M5" s="31" cm="1">
         <f t="array" ref="M5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -2971,13 +2974,13 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D6" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -3013,7 +3016,7 @@
       </c>
       <c r="L6" s="31" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M6" s="31" cm="1">
         <f t="array" ref="M6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -3122,13 +3125,13 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D7" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -3164,7 +3167,7 @@
       </c>
       <c r="L7" s="31" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M7" s="31" cm="1">
         <f t="array" ref="M7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -3273,13 +3276,13 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -3315,7 +3318,7 @@
       </c>
       <c r="L8" s="31" t="str" cm="1">
         <f t="array" ref="L8">_xlfn.XLOOKUP($A8,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M8" s="31" cm="1">
         <f t="array" ref="M8">_xlfn.XLOOKUP($A8,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -3424,13 +3427,13 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D9" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -3466,7 +3469,7 @@
       </c>
       <c r="L9" s="31" t="str" cm="1">
         <f t="array" ref="L9">_xlfn.XLOOKUP($A9,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M9" s="31" cm="1">
         <f t="array" ref="M9">_xlfn.XLOOKUP($A9,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -3575,13 +3578,13 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D10" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -3617,7 +3620,7 @@
       </c>
       <c r="L10" s="31" t="str" cm="1">
         <f t="array" ref="L10">_xlfn.XLOOKUP($A10,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M10" s="31" cm="1">
         <f t="array" ref="M10">_xlfn.XLOOKUP($A10,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -3726,13 +3729,13 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D11" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -3768,7 +3771,7 @@
       </c>
       <c r="L11" s="31" t="str" cm="1">
         <f t="array" ref="L11">_xlfn.XLOOKUP($A11,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M11" s="31" cm="1">
         <f t="array" ref="M11">_xlfn.XLOOKUP($A11,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -3877,13 +3880,13 @@
     </row>
     <row r="12" spans="1:38" ht="17" thickBot="1">
       <c r="A12" s="75" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D12" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -3919,7 +3922,7 @@
       </c>
       <c r="L12" s="31" t="str" cm="1">
         <f t="array" ref="L12">_xlfn.XLOOKUP($A12,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M12" s="31" cm="1">
         <f t="array" ref="M12">_xlfn.XLOOKUP($A12,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -4028,13 +4031,13 @@
     </row>
     <row r="13" spans="1:38" ht="17" thickBot="1">
       <c r="A13" s="75" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D13" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -4070,7 +4073,7 @@
       </c>
       <c r="L13" s="31" t="str" cm="1">
         <f t="array" ref="L13">_xlfn.XLOOKUP($A13,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M13" s="31" cm="1">
         <f t="array" ref="M13">_xlfn.XLOOKUP($A13,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -4179,13 +4182,13 @@
     </row>
     <row r="14" spans="1:38" ht="17" thickBot="1">
       <c r="A14" s="75" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D14" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -4221,7 +4224,7 @@
       </c>
       <c r="L14" s="31" t="str" cm="1">
         <f t="array" ref="L14">_xlfn.XLOOKUP($A14,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M14" s="31" cm="1">
         <f t="array" ref="M14">_xlfn.XLOOKUP($A14,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -4330,13 +4333,13 @@
     </row>
     <row r="15" spans="1:38" ht="17" thickBot="1">
       <c r="A15" s="75" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D15" s="24" t="str">
         <f>IF(TestCaseConfig!$B$3="Yes","Yes","No")</f>
@@ -4372,7 +4375,7 @@
       </c>
       <c r="L15" s="31" t="str" cm="1">
         <f t="array" ref="L15">_xlfn.XLOOKUP($A15,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pet and Live</v>
       </c>
       <c r="M15" s="31" cm="1">
         <f t="array" ref="M15">_xlfn.XLOOKUP($A15,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -7172,7 +7175,7 @@
         <v>110</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>122</v>
@@ -7193,7 +7196,7 @@
         <v>141</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M1" s="27" t="s">
         <v>196</v>
@@ -7271,7 +7274,7 @@
         <v>102</v>
       </c>
       <c r="AL1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM1" s="20" t="s">
         <v>73</v>
@@ -7279,10 +7282,10 @@
     </row>
     <row r="2" spans="1:39" ht="17" thickBot="1">
       <c r="A2" s="63" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C2" s="32" t="s">
         <v>35</v>
@@ -7434,10 +7437,10 @@
     </row>
     <row r="3" spans="1:39" ht="17" thickBot="1">
       <c r="A3" s="63" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C3" s="32" t="s">
         <v>35</v>
@@ -7589,10 +7592,10 @@
     </row>
     <row r="4" spans="1:39" ht="17" thickBot="1">
       <c r="A4" s="63" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>35</v>
@@ -7744,10 +7747,10 @@
     </row>
     <row r="5" spans="1:39" ht="17" thickBot="1">
       <c r="A5" s="63" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>35</v>
@@ -7899,10 +7902,10 @@
     </row>
     <row r="6" spans="1:39" ht="17" thickBot="1">
       <c r="A6" s="63" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>35</v>
@@ -8054,10 +8057,10 @@
     </row>
     <row r="7" spans="1:39" ht="17" thickBot="1">
       <c r="A7" s="63" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>35</v>
@@ -8243,7 +8246,7 @@
         <v>110</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>122</v>
@@ -8264,7 +8267,7 @@
         <v>141</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M1" s="27" t="s">
         <v>196</v>
@@ -8342,21 +8345,21 @@
         <v>102</v>
       </c>
       <c r="AL1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM1" s="20" t="s">
         <v>73</v>
       </c>
       <c r="AN1" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:40" ht="17" thickBot="1">
       <c r="A2" s="64" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C2" s="32" t="s">
         <v>35</v>
@@ -8512,10 +8515,10 @@
     </row>
     <row r="3" spans="1:40" ht="17" thickBot="1">
       <c r="A3" s="64" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C3" s="32" t="s">
         <v>35</v>
@@ -8671,10 +8674,10 @@
     </row>
     <row r="4" spans="1:40" ht="17" thickBot="1">
       <c r="A4" s="64" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>35</v>
@@ -8830,10 +8833,10 @@
     </row>
     <row r="5" spans="1:40" ht="17" thickBot="1">
       <c r="A5" s="64" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>35</v>
@@ -8989,10 +8992,10 @@
     </row>
     <row r="6" spans="1:40" ht="17" thickBot="1">
       <c r="A6" s="64" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>35</v>
@@ -9148,10 +9151,10 @@
     </row>
     <row r="7" spans="1:40" ht="17" thickBot="1">
       <c r="A7" s="64" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>35</v>
@@ -9389,7 +9392,7 @@
         <v>141</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L1" s="27" t="s">
         <v>196</v>
@@ -9467,7 +9470,7 @@
         <v>102</v>
       </c>
       <c r="AK1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL1" s="20" t="s">
         <v>73</v>
@@ -9475,13 +9478,13 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="68" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D2" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -9626,10 +9629,10 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="69" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C3" s="32" t="s">
         <v>39</v>
@@ -9777,13 +9780,13 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="69" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D4" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -9928,13 +9931,13 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="69" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D5" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -10079,13 +10082,13 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="69" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D6" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -10230,13 +10233,13 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="69" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D7" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -10381,13 +10384,13 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="69" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D8" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -10532,10 +10535,10 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="69" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C9" s="32" t="s">
         <v>39</v>
@@ -10683,13 +10686,13 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="69" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D10" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -10834,13 +10837,13 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="69" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D11" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -10985,13 +10988,13 @@
     </row>
     <row r="12" spans="1:38" ht="17" thickBot="1">
       <c r="A12" s="69" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D12" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -11136,13 +11139,13 @@
     </row>
     <row r="13" spans="1:38" ht="17" thickBot="1">
       <c r="A13" s="69" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D13" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -11323,7 +11326,7 @@
         <v>110</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>122</v>
@@ -11344,7 +11347,7 @@
         <v>141</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M1" s="27" t="s">
         <v>196</v>
@@ -11422,7 +11425,7 @@
         <v>102</v>
       </c>
       <c r="AL1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM1" s="20" t="s">
         <v>73</v>
@@ -11430,7 +11433,7 @@
     </row>
     <row r="2" spans="1:39" ht="17" thickBot="1">
       <c r="A2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>27</v>
@@ -11585,7 +11588,7 @@
     </row>
     <row r="3" spans="1:39" ht="17" thickBot="1">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B3" s="43" t="s">
         <v>27</v>
@@ -11740,7 +11743,7 @@
     </row>
     <row r="4" spans="1:39" ht="17" thickBot="1">
       <c r="A4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B4" s="43" t="s">
         <v>27</v>
@@ -11895,7 +11898,7 @@
     </row>
     <row r="5" spans="1:39" ht="17" thickBot="1">
       <c r="A5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>27</v>
@@ -12050,7 +12053,7 @@
     </row>
     <row r="6" spans="1:39" ht="17" thickBot="1">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B6" s="43" t="s">
         <v>27</v>
@@ -12205,7 +12208,7 @@
     </row>
     <row r="7" spans="1:39" ht="17" thickBot="1">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B7" s="43" t="s">
         <v>27</v>
@@ -12360,7 +12363,7 @@
     </row>
     <row r="8" spans="1:39" ht="17" thickBot="1">
       <c r="A8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B8" s="43" t="s">
         <v>27</v>
@@ -12515,7 +12518,7 @@
     </row>
     <row r="9" spans="1:39" ht="17" thickBot="1">
       <c r="A9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B9" s="43" t="s">
         <v>27</v>
@@ -12670,7 +12673,7 @@
     </row>
     <row r="10" spans="1:39" ht="17" thickBot="1">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B10" s="43" t="s">
         <v>27</v>
@@ -12825,7 +12828,7 @@
     </row>
     <row r="11" spans="1:39" ht="17" thickBot="1">
       <c r="A11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B11" s="43" t="s">
         <v>27</v>
@@ -13015,7 +13018,7 @@
         <v>110</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>122</v>
@@ -13036,7 +13039,7 @@
         <v>141</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M1" s="27" t="s">
         <v>196</v>
@@ -13114,7 +13117,7 @@
         <v>102</v>
       </c>
       <c r="AL1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM1" s="20" t="s">
         <v>73</v>
@@ -13122,7 +13125,7 @@
     </row>
     <row r="2" spans="1:39" ht="17" thickBot="1">
       <c r="A2" s="65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>45</v>
@@ -13277,7 +13280,7 @@
     </row>
     <row r="3" spans="1:39" ht="17" thickBot="1">
       <c r="A3" s="65" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B3" s="43" t="s">
         <v>45</v>
@@ -13432,7 +13435,7 @@
     </row>
     <row r="4" spans="1:39" ht="17" thickBot="1">
       <c r="A4" s="65" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B4" s="43" t="s">
         <v>45</v>
@@ -13587,7 +13590,7 @@
     </row>
     <row r="5" spans="1:39" ht="17" thickBot="1">
       <c r="A5" s="65" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>45</v>
@@ -13742,7 +13745,7 @@
     </row>
     <row r="6" spans="1:39" ht="17" thickBot="1">
       <c r="A6" s="65" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B6" s="43" t="s">
         <v>45</v>
@@ -13897,7 +13900,7 @@
     </row>
     <row r="7" spans="1:39" ht="17" thickBot="1">
       <c r="A7" s="65" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B7" s="43" t="s">
         <v>45</v>
@@ -14052,7 +14055,7 @@
     </row>
     <row r="8" spans="1:39" ht="17" thickBot="1">
       <c r="A8" s="65" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B8" s="43" t="s">
         <v>45</v>
@@ -14207,7 +14210,7 @@
     </row>
     <row r="9" spans="1:39" ht="17" thickBot="1">
       <c r="A9" s="65" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B9" s="43" t="s">
         <v>45</v>
@@ -14362,7 +14365,7 @@
     </row>
     <row r="10" spans="1:39" ht="17" thickBot="1">
       <c r="A10" s="65" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B10" s="43" t="s">
         <v>45</v>
@@ -14517,7 +14520,7 @@
     </row>
     <row r="11" spans="1:39" ht="17" thickBot="1">
       <c r="A11" s="65" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B11" s="43" t="s">
         <v>45</v>
@@ -14722,7 +14725,7 @@
         <v>141</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L1" s="27" t="s">
         <v>196</v>
@@ -14800,7 +14803,7 @@
         <v>102</v>
       </c>
       <c r="AK1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL1" s="20" t="s">
         <v>73</v>
@@ -14808,7 +14811,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="66" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>44</v>
@@ -14959,7 +14962,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="66" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B3" s="43" t="s">
         <v>44</v>
@@ -15110,7 +15113,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="66" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B4" s="43" t="s">
         <v>44</v>
@@ -15261,7 +15264,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>44</v>
@@ -15412,7 +15415,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="66" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B6" s="43" t="s">
         <v>44</v>
@@ -15563,7 +15566,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="66" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B7" s="43" t="s">
         <v>44</v>
@@ -15714,7 +15717,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="66" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B8" s="43" t="s">
         <v>44</v>
@@ -15865,7 +15868,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="66" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B9" s="43" t="s">
         <v>44</v>
@@ -16016,7 +16019,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="66" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B10" s="43" t="s">
         <v>44</v>
@@ -16167,7 +16170,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="66" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B11" s="43" t="s">
         <v>44</v>
@@ -16318,7 +16321,7 @@
     </row>
     <row r="12" spans="1:38" ht="17" thickBot="1">
       <c r="A12" s="66" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B12" s="43" t="s">
         <v>44</v>
@@ -16469,7 +16472,7 @@
     </row>
     <row r="13" spans="1:38" ht="17" thickBot="1">
       <c r="A13" s="66" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B13" s="43" t="s">
         <v>44</v>
@@ -16650,7 +16653,7 @@
         <v>110</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>122</v>
@@ -16671,7 +16674,7 @@
         <v>141</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M1" s="27" t="s">
         <v>196</v>
@@ -16749,7 +16752,7 @@
         <v>102</v>
       </c>
       <c r="AL1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM1" s="20" t="s">
         <v>73</v>
@@ -16757,7 +16760,7 @@
     </row>
     <row r="2" spans="1:39" ht="16" thickBot="1">
       <c r="A2" s="67" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>87</v>
@@ -16912,7 +16915,7 @@
     </row>
     <row r="3" spans="1:39" ht="16" thickBot="1">
       <c r="A3" s="67" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B3" s="43" t="s">
         <v>87</v>
@@ -17067,7 +17070,7 @@
     </row>
     <row r="4" spans="1:39" ht="16" thickBot="1">
       <c r="A4" s="67" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B4" s="43" t="s">
         <v>87</v>
@@ -17222,7 +17225,7 @@
     </row>
     <row r="5" spans="1:39" ht="16" thickBot="1">
       <c r="A5" s="67" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>87</v>
@@ -17412,7 +17415,7 @@
         <v>110</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F1" s="20" t="s">
         <v>122</v>
@@ -17433,7 +17436,7 @@
         <v>141</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M1" s="27" t="s">
         <v>196</v>
@@ -17511,7 +17514,7 @@
         <v>102</v>
       </c>
       <c r="AL1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM1" s="20" t="s">
         <v>73</v>
@@ -17519,13 +17522,13 @@
     </row>
     <row r="2" spans="1:39" ht="16" thickBot="1">
       <c r="A2" s="70" t="s">
-        <v>402</v>
+        <v>339</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D2" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17533,7 +17536,7 @@
       </c>
       <c r="E2" s="31" t="str" cm="1">
         <f t="array" ref="E2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>Cares</v>
+        <v>CARE</v>
       </c>
       <c r="F2" s="31" t="str" cm="1">
         <f t="array" ref="F2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -17674,13 +17677,13 @@
     </row>
     <row r="3" spans="1:39" ht="16" thickBot="1">
       <c r="A3" s="71" t="s">
-        <v>403</v>
+        <v>340</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D3" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17688,7 +17691,7 @@
       </c>
       <c r="E3" s="31" t="str" cm="1">
         <f t="array" ref="E3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>Cares</v>
+        <v>CARE</v>
       </c>
       <c r="F3" s="31" t="str" cm="1">
         <f t="array" ref="F3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -17724,7 +17727,7 @@
       </c>
       <c r="N3" s="31" cm="1">
         <f t="array" ref="N3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(N$1,dataRowRange,ActualDataRange))</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O3" s="31" t="str" cm="1">
         <f t="array" ref="O3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(O$1,dataRowRange,ActualDataRange))</f>
@@ -17829,13 +17832,13 @@
     </row>
     <row r="4" spans="1:39" ht="16" thickBot="1">
       <c r="A4" s="71" t="s">
-        <v>404</v>
+        <v>341</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D4" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17843,7 +17846,7 @@
       </c>
       <c r="E4" s="31" t="str" cm="1">
         <f t="array" ref="E4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>Cares</v>
+        <v>CARE</v>
       </c>
       <c r="F4" s="31" t="str" cm="1">
         <f t="array" ref="F4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -17984,13 +17987,13 @@
     </row>
     <row r="5" spans="1:39" ht="16" thickBot="1">
       <c r="A5" s="71" t="s">
-        <v>405</v>
+        <v>342</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D5" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17998,7 +18001,7 @@
       </c>
       <c r="E5" s="31" t="str" cm="1">
         <f t="array" ref="E5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>Cares</v>
+        <v>CARE</v>
       </c>
       <c r="F5" s="31" t="str" cm="1">
         <f t="array" ref="F5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -18139,13 +18142,13 @@
     </row>
     <row r="6" spans="1:39" ht="16" thickBot="1">
       <c r="A6" s="71" t="s">
-        <v>406</v>
+        <v>343</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D6" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -18153,7 +18156,7 @@
       </c>
       <c r="E6" s="31" t="str" cm="1">
         <f t="array" ref="E6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>Cares</v>
+        <v>CARE</v>
       </c>
       <c r="F6" s="31" t="str" cm="1">
         <f t="array" ref="F6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -18189,7 +18192,7 @@
       </c>
       <c r="N6" s="31" cm="1">
         <f t="array" ref="N6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(N$1,dataRowRange,ActualDataRange))</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O6" s="31" t="str" cm="1">
         <f t="array" ref="O6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(O$1,dataRowRange,ActualDataRange))</f>
@@ -18294,13 +18297,13 @@
     </row>
     <row r="7" spans="1:39" ht="16" thickBot="1">
       <c r="A7" s="71" t="s">
-        <v>407</v>
+        <v>344</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D7" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -18308,7 +18311,7 @@
       </c>
       <c r="E7" s="31" t="str" cm="1">
         <f t="array" ref="E7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>Cares</v>
+        <v>CARE</v>
       </c>
       <c r="F7" s="31" t="str" cm="1">
         <f t="array" ref="F7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -18482,7 +18485,7 @@
         <v>195</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="32.15" customHeight="1">
@@ -18595,13 +18598,13 @@
     </row>
     <row r="8" spans="1:5" ht="16">
       <c r="A8" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>121</v>
@@ -18613,16 +18616,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E9" s="41">
         <f>COUNTA(GBParcel16Oz!A:A)-1</f>
@@ -18631,16 +18634,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E10" s="41">
         <f>COUNTA(GBParcel!A:A)-1</f>
@@ -18649,16 +18652,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E11" s="41">
         <f>COUNTA(GBPetLive!A:A)-1</f>
@@ -18667,16 +18670,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E12" s="41">
         <f>COUNTA(GBPerishable!A:A)-1</f>
@@ -18685,16 +18688,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E13" s="41">
         <f>COUNTA(GBPharma!A:A)-1</f>
@@ -18703,16 +18706,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C14" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>207</v>
       </c>
       <c r="E14" s="41">
         <f>COUNTA(GBMedical!A:A)-1</f>
@@ -18721,16 +18724,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E15" s="41">
         <f>COUNTA(GBSpecialty!A:A)-1</f>
@@ -18739,16 +18742,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E16" s="41">
         <f>COUNTA(GBHumanRemains!A:A)-1</f>
@@ -18832,7 +18835,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D1" s="20" t="s">
         <v>122</v>
@@ -18853,7 +18856,7 @@
         <v>141</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K1" s="20" t="s">
         <v>196</v>
@@ -18931,13 +18934,13 @@
         <v>102</v>
       </c>
       <c r="AJ1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK1" s="20" t="s">
         <v>73</v>
       </c>
       <c r="AL1" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:38">
@@ -18973,13 +18976,13 @@
         <v>16</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>197</v>
+        <v>407</v>
       </c>
       <c r="L2" s="44">
         <v>30</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N2" s="44">
         <v>1</v>
@@ -19048,7 +19051,7 @@
         <v>106</v>
       </c>
       <c r="AJ2" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK2" s="44"/>
     </row>
@@ -19085,13 +19088,13 @@
         <v>16</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>197</v>
+        <v>407</v>
       </c>
       <c r="L3" s="44">
         <v>90</v>
       </c>
       <c r="M3" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N3" s="44">
         <v>1</v>
@@ -19160,7 +19163,7 @@
         <v>106</v>
       </c>
       <c r="AJ3" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK3" s="44"/>
     </row>
@@ -19197,13 +19200,13 @@
         <v>16</v>
       </c>
       <c r="K4" s="44" t="s">
+        <v>407</v>
+      </c>
+      <c r="L4" s="44">
+        <v>10</v>
+      </c>
+      <c r="M4" s="44" t="s">
         <v>197</v>
-      </c>
-      <c r="L4" s="44">
-        <v>10</v>
-      </c>
-      <c r="M4" s="44" t="s">
-        <v>198</v>
       </c>
       <c r="N4" s="44">
         <v>1</v>
@@ -19272,7 +19275,7 @@
         <v>106</v>
       </c>
       <c r="AJ4" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK4" s="44"/>
     </row>
@@ -19309,13 +19312,13 @@
         <v>16</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>197</v>
+        <v>407</v>
       </c>
       <c r="L5" s="44">
         <v>30</v>
       </c>
       <c r="M5" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N5" s="44">
         <v>1</v>
@@ -19381,10 +19384,10 @@
         <v>55055</v>
       </c>
       <c r="AI5" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ5" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK5" s="44"/>
     </row>
@@ -19421,13 +19424,13 @@
         <v>16</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>197</v>
+        <v>407</v>
       </c>
       <c r="L6" s="44">
         <v>90</v>
       </c>
       <c r="M6" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N6" s="44">
         <v>1</v>
@@ -19493,10 +19496,10 @@
         <v>55055</v>
       </c>
       <c r="AI6" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ6" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK6" s="44"/>
     </row>
@@ -19533,13 +19536,13 @@
         <v>16</v>
       </c>
       <c r="K7" s="44" t="s">
+        <v>407</v>
+      </c>
+      <c r="L7" s="44">
+        <v>10</v>
+      </c>
+      <c r="M7" s="44" t="s">
         <v>197</v>
-      </c>
-      <c r="L7" s="44">
-        <v>10</v>
-      </c>
-      <c r="M7" s="44" t="s">
-        <v>198</v>
       </c>
       <c r="N7" s="44">
         <v>1</v>
@@ -19605,10 +19608,10 @@
         <v>55055</v>
       </c>
       <c r="AI7" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ7" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK7" s="44"/>
     </row>
@@ -19645,7 +19648,7 @@
         <v>57</v>
       </c>
       <c r="K8" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L8" s="44">
         <v>10</v>
@@ -19720,7 +19723,7 @@
         <v>106</v>
       </c>
       <c r="AJ8" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK8" s="44"/>
     </row>
@@ -19757,7 +19760,7 @@
         <v>115</v>
       </c>
       <c r="K9" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L9" s="44">
         <v>10</v>
@@ -19832,7 +19835,7 @@
         <v>106</v>
       </c>
       <c r="AJ9" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK9" s="44"/>
     </row>
@@ -19869,7 +19872,7 @@
         <v>116</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L10" s="44">
         <v>10</v>
@@ -19944,7 +19947,7 @@
         <v>106</v>
       </c>
       <c r="AJ10" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK10" s="44"/>
     </row>
@@ -19981,7 +19984,7 @@
         <v>69</v>
       </c>
       <c r="K11" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L11" s="44">
         <v>10</v>
@@ -20056,7 +20059,7 @@
         <v>106</v>
       </c>
       <c r="AJ11" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK11" s="44"/>
     </row>
@@ -20093,7 +20096,7 @@
         <v>117</v>
       </c>
       <c r="K12" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L12" s="44">
         <v>10</v>
@@ -20168,7 +20171,7 @@
         <v>106</v>
       </c>
       <c r="AJ12" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK12" s="44"/>
     </row>
@@ -20205,7 +20208,7 @@
         <v>57</v>
       </c>
       <c r="K13" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L13" s="44">
         <v>10</v>
@@ -20277,10 +20280,10 @@
         <v>55055</v>
       </c>
       <c r="AI13" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ13" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK13" s="44"/>
     </row>
@@ -20317,7 +20320,7 @@
         <v>115</v>
       </c>
       <c r="K14" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L14" s="44">
         <v>10</v>
@@ -20389,10 +20392,10 @@
         <v>55055</v>
       </c>
       <c r="AI14" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ14" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK14" s="44"/>
     </row>
@@ -20429,7 +20432,7 @@
         <v>116</v>
       </c>
       <c r="K15" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L15" s="44">
         <v>10</v>
@@ -20501,10 +20504,10 @@
         <v>55055</v>
       </c>
       <c r="AI15" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ15" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK15" s="44"/>
     </row>
@@ -20541,7 +20544,7 @@
         <v>69</v>
       </c>
       <c r="K16" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L16" s="44">
         <v>10</v>
@@ -20613,10 +20616,10 @@
         <v>55055</v>
       </c>
       <c r="AI16" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ16" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK16" s="44"/>
     </row>
@@ -20653,7 +20656,7 @@
         <v>117</v>
       </c>
       <c r="K17" s="44" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="L17" s="44">
         <v>10</v>
@@ -20725,10 +20728,10 @@
         <v>55055</v>
       </c>
       <c r="AI17" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ17" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK17" s="44"/>
     </row>
@@ -20765,7 +20768,7 @@
         <v>54</v>
       </c>
       <c r="K18" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L18" s="44">
         <v>10</v>
@@ -20840,7 +20843,7 @@
         <v>106</v>
       </c>
       <c r="AJ18" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK18" s="44"/>
     </row>
@@ -20877,7 +20880,7 @@
         <v>175</v>
       </c>
       <c r="K19" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L19" s="44">
         <v>10</v>
@@ -20952,7 +20955,7 @@
         <v>106</v>
       </c>
       <c r="AJ19" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK19" s="44"/>
     </row>
@@ -20989,7 +20992,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L20" s="44">
         <v>10</v>
@@ -21064,7 +21067,7 @@
         <v>106</v>
       </c>
       <c r="AJ20" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK20" s="44"/>
     </row>
@@ -21101,7 +21104,7 @@
         <v>193</v>
       </c>
       <c r="K21" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L21" s="44">
         <v>10</v>
@@ -21176,7 +21179,7 @@
         <v>106</v>
       </c>
       <c r="AJ21" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK21" s="44"/>
     </row>
@@ -21213,7 +21216,7 @@
         <v>194</v>
       </c>
       <c r="K22" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L22" s="44">
         <v>10</v>
@@ -21288,7 +21291,7 @@
         <v>106</v>
       </c>
       <c r="AJ22" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK22" s="44"/>
     </row>
@@ -21325,7 +21328,7 @@
         <v>54</v>
       </c>
       <c r="K23" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L23" s="44">
         <v>10</v>
@@ -21397,10 +21400,10 @@
         <v>55055</v>
       </c>
       <c r="AI23" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ23" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK23" s="44"/>
     </row>
@@ -21437,7 +21440,7 @@
         <v>175</v>
       </c>
       <c r="K24" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L24" s="44">
         <v>10</v>
@@ -21509,10 +21512,10 @@
         <v>55055</v>
       </c>
       <c r="AI24" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ24" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK24" s="44"/>
     </row>
@@ -21549,7 +21552,7 @@
         <v>63</v>
       </c>
       <c r="K25" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L25" s="44">
         <v>10</v>
@@ -21621,10 +21624,10 @@
         <v>55055</v>
       </c>
       <c r="AI25" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ25" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK25" s="44"/>
     </row>
@@ -21661,7 +21664,7 @@
         <v>193</v>
       </c>
       <c r="K26" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L26" s="44">
         <v>10</v>
@@ -21733,10 +21736,10 @@
         <v>55055</v>
       </c>
       <c r="AI26" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ26" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK26" s="44"/>
     </row>
@@ -21773,7 +21776,7 @@
         <v>194</v>
       </c>
       <c r="K27" s="44" t="s">
-        <v>197</v>
+        <v>298</v>
       </c>
       <c r="L27" s="44">
         <v>10</v>
@@ -21845,10 +21848,10 @@
         <v>55055</v>
       </c>
       <c r="AI27" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ27" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK27" s="44"/>
     </row>
@@ -21885,7 +21888,7 @@
         <v>177</v>
       </c>
       <c r="K28" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L28" s="44">
         <v>10</v>
@@ -21960,7 +21963,7 @@
         <v>106</v>
       </c>
       <c r="AJ28" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK28" s="44"/>
     </row>
@@ -21997,7 +22000,7 @@
         <v>178</v>
       </c>
       <c r="K29" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L29" s="44">
         <v>10</v>
@@ -22072,7 +22075,7 @@
         <v>106</v>
       </c>
       <c r="AJ29" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK29" s="44"/>
     </row>
@@ -22109,7 +22112,7 @@
         <v>179</v>
       </c>
       <c r="K30" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L30" s="44">
         <v>10</v>
@@ -22184,7 +22187,7 @@
         <v>106</v>
       </c>
       <c r="AJ30" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK30" s="44"/>
     </row>
@@ -22221,7 +22224,7 @@
         <v>180</v>
       </c>
       <c r="K31" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L31" s="44">
         <v>10</v>
@@ -22296,7 +22299,7 @@
         <v>106</v>
       </c>
       <c r="AJ31" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK31" s="44"/>
     </row>
@@ -22333,7 +22336,7 @@
         <v>181</v>
       </c>
       <c r="K32" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L32" s="44">
         <v>10</v>
@@ -22408,7 +22411,7 @@
         <v>106</v>
       </c>
       <c r="AJ32" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK32" s="44"/>
     </row>
@@ -22445,7 +22448,7 @@
         <v>182</v>
       </c>
       <c r="K33" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L33" s="44">
         <v>10</v>
@@ -22520,7 +22523,7 @@
         <v>106</v>
       </c>
       <c r="AJ33" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK33" s="44"/>
     </row>
@@ -22557,7 +22560,7 @@
         <v>177</v>
       </c>
       <c r="K34" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L34" s="44">
         <v>10</v>
@@ -22629,10 +22632,10 @@
         <v>55055</v>
       </c>
       <c r="AI34" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ34" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK34" s="44"/>
     </row>
@@ -22669,7 +22672,7 @@
         <v>178</v>
       </c>
       <c r="K35" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L35" s="44">
         <v>10</v>
@@ -22741,10 +22744,10 @@
         <v>55055</v>
       </c>
       <c r="AI35" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ35" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK35" s="44"/>
     </row>
@@ -22781,7 +22784,7 @@
         <v>179</v>
       </c>
       <c r="K36" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L36" s="44">
         <v>10</v>
@@ -22853,10 +22856,10 @@
         <v>55055</v>
       </c>
       <c r="AI36" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ36" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK36" s="44"/>
     </row>
@@ -22893,7 +22896,7 @@
         <v>180</v>
       </c>
       <c r="K37" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L37" s="44">
         <v>10</v>
@@ -22965,10 +22968,10 @@
         <v>55055</v>
       </c>
       <c r="AI37" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ37" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK37" s="44"/>
     </row>
@@ -23005,7 +23008,7 @@
         <v>181</v>
       </c>
       <c r="K38" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L38" s="44">
         <v>10</v>
@@ -23077,10 +23080,10 @@
         <v>55055</v>
       </c>
       <c r="AI38" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ38" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK38" s="44"/>
     </row>
@@ -23117,7 +23120,7 @@
         <v>182</v>
       </c>
       <c r="K39" s="44" t="s">
-        <v>197</v>
+        <v>305</v>
       </c>
       <c r="L39" s="44">
         <v>10</v>
@@ -23189,10 +23192,10 @@
         <v>55055</v>
       </c>
       <c r="AI39" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ39" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK39" s="44"/>
     </row>
@@ -23229,7 +23232,7 @@
         <v>183</v>
       </c>
       <c r="K40" s="44" t="s">
-        <v>197</v>
+        <v>306</v>
       </c>
       <c r="L40" s="44">
         <v>10</v>
@@ -23304,7 +23307,7 @@
         <v>106</v>
       </c>
       <c r="AJ40" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK40" s="44"/>
     </row>
@@ -23341,7 +23344,7 @@
         <v>184</v>
       </c>
       <c r="K41" s="44" t="s">
-        <v>197</v>
+        <v>306</v>
       </c>
       <c r="L41" s="44">
         <v>10</v>
@@ -23416,7 +23419,7 @@
         <v>106</v>
       </c>
       <c r="AJ41" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK41" s="44"/>
     </row>
@@ -23453,7 +23456,7 @@
         <v>183</v>
       </c>
       <c r="K42" s="44" t="s">
-        <v>197</v>
+        <v>306</v>
       </c>
       <c r="L42" s="44">
         <v>10</v>
@@ -23525,10 +23528,10 @@
         <v>55055</v>
       </c>
       <c r="AI42" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ42" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK42" s="44"/>
     </row>
@@ -23565,7 +23568,7 @@
         <v>184</v>
       </c>
       <c r="K43" s="44" t="s">
-        <v>197</v>
+        <v>306</v>
       </c>
       <c r="L43" s="44">
         <v>10</v>
@@ -23637,10 +23640,10 @@
         <v>55055</v>
       </c>
       <c r="AI43" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ43" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK43" s="44"/>
     </row>
@@ -23677,7 +23680,7 @@
         <v>186</v>
       </c>
       <c r="K44" s="44" t="s">
-        <v>197</v>
+        <v>408</v>
       </c>
       <c r="L44" s="44">
         <v>10</v>
@@ -23752,7 +23755,7 @@
         <v>106</v>
       </c>
       <c r="AJ44" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK44" s="44"/>
     </row>
@@ -23789,7 +23792,7 @@
         <v>187</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>197</v>
+        <v>408</v>
       </c>
       <c r="L45" s="44">
         <v>10</v>
@@ -23864,7 +23867,7 @@
         <v>106</v>
       </c>
       <c r="AJ45" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK45" s="44"/>
     </row>
@@ -23901,7 +23904,7 @@
         <v>188</v>
       </c>
       <c r="K46" s="44" t="s">
-        <v>197</v>
+        <v>408</v>
       </c>
       <c r="L46" s="44">
         <v>10</v>
@@ -23976,7 +23979,7 @@
         <v>106</v>
       </c>
       <c r="AJ46" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK46" s="44"/>
     </row>
@@ -24013,7 +24016,7 @@
         <v>186</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>197</v>
+        <v>408</v>
       </c>
       <c r="L47" s="44">
         <v>10</v>
@@ -24085,10 +24088,10 @@
         <v>55055</v>
       </c>
       <c r="AI47" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ47" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK47" s="44"/>
     </row>
@@ -24125,7 +24128,7 @@
         <v>187</v>
       </c>
       <c r="K48" s="44" t="s">
-        <v>197</v>
+        <v>408</v>
       </c>
       <c r="L48" s="44">
         <v>10</v>
@@ -24197,10 +24200,10 @@
         <v>55055</v>
       </c>
       <c r="AI48" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ48" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK48" s="44"/>
     </row>
@@ -24237,7 +24240,7 @@
         <v>188</v>
       </c>
       <c r="K49" s="44" t="s">
-        <v>197</v>
+        <v>408</v>
       </c>
       <c r="L49" s="44">
         <v>10</v>
@@ -24309,10 +24312,10 @@
         <v>55055</v>
       </c>
       <c r="AI49" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ49" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK49" s="44"/>
     </row>
@@ -24322,10 +24325,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_Bird_Domestic</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D50" s="46" t="s">
         <v>125</v>
@@ -24346,10 +24349,10 @@
         <v>142</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K50" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L50" s="44">
         <v>10</v>
@@ -24424,7 +24427,7 @@
         <v>106</v>
       </c>
       <c r="AJ50" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK50" s="44"/>
     </row>
@@ -24434,10 +24437,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_DayOldChicks_Domestic</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D51" s="46" t="s">
         <v>125</v>
@@ -24458,10 +24461,10 @@
         <v>142</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K51" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L51" s="44">
         <v>10</v>
@@ -24536,7 +24539,7 @@
         <v>106</v>
       </c>
       <c r="AJ51" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK51" s="44"/>
     </row>
@@ -24546,10 +24549,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_LabAnimalse.g.Mice_Domestic</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D52" s="46" t="s">
         <v>125</v>
@@ -24570,10 +24573,10 @@
         <v>142</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K52" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L52" s="44">
         <v>10</v>
@@ -24648,7 +24651,7 @@
         <v>106</v>
       </c>
       <c r="AJ52" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK52" s="44"/>
     </row>
@@ -24658,10 +24661,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_OtherWarmBloodedAnimal_Domestic</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D53" s="46" t="s">
         <v>125</v>
@@ -24682,10 +24685,10 @@
         <v>142</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K53" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L53" s="44">
         <v>10</v>
@@ -24760,7 +24763,7 @@
         <v>106</v>
       </c>
       <c r="AJ53" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK53" s="44"/>
     </row>
@@ -24770,10 +24773,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_ReptileAmphibianetc._Domestic</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D54" s="46" t="s">
         <v>125</v>
@@ -24794,10 +24797,10 @@
         <v>142</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K54" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L54" s="44">
         <v>10</v>
@@ -24872,7 +24875,7 @@
         <v>106</v>
       </c>
       <c r="AJ54" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK54" s="44"/>
     </row>
@@ -24882,10 +24885,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_TropicalFish_Domestic</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D55" s="46" t="s">
         <v>125</v>
@@ -24906,10 +24909,10 @@
         <v>142</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K55" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L55" s="44">
         <v>10</v>
@@ -24984,7 +24987,7 @@
         <v>106</v>
       </c>
       <c r="AJ55" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK55" s="44"/>
     </row>
@@ -24994,10 +24997,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_HatchingEggs_Domestic</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D56" s="46" t="s">
         <v>125</v>
@@ -25018,10 +25021,10 @@
         <v>142</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K56" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L56" s="44">
         <v>10</v>
@@ -25096,7 +25099,7 @@
         <v>106</v>
       </c>
       <c r="AJ56" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AK56" s="44"/>
     </row>
@@ -25106,10 +25109,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_Bird_International</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D57" s="46" t="s">
         <v>125</v>
@@ -25130,10 +25133,10 @@
         <v>142</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K57" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L57" s="44">
         <v>10</v>
@@ -25205,10 +25208,10 @@
         <v>55055</v>
       </c>
       <c r="AI57" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ57" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK57" s="44"/>
     </row>
@@ -25218,10 +25221,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_DayOldChicks_International</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D58" s="46" t="s">
         <v>125</v>
@@ -25242,10 +25245,10 @@
         <v>142</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K58" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L58" s="44">
         <v>10</v>
@@ -25317,10 +25320,10 @@
         <v>55055</v>
       </c>
       <c r="AI58" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ58" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK58" s="44"/>
     </row>
@@ -25330,10 +25333,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_LabAnimalse.g.Mice_International</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D59" s="46" t="s">
         <v>125</v>
@@ -25354,10 +25357,10 @@
         <v>142</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K59" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L59" s="44">
         <v>10</v>
@@ -25429,10 +25432,10 @@
         <v>55055</v>
       </c>
       <c r="AI59" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ59" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK59" s="44"/>
     </row>
@@ -25442,10 +25445,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_OtherWarmBloodedAnimal_International</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D60" s="46" t="s">
         <v>125</v>
@@ -25466,10 +25469,10 @@
         <v>142</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K60" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L60" s="44">
         <v>10</v>
@@ -25541,10 +25544,10 @@
         <v>55055</v>
       </c>
       <c r="AI60" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ60" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK60" s="44"/>
     </row>
@@ -25554,10 +25557,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_ReptileAmphibianetc._International</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D61" s="46" t="s">
         <v>125</v>
@@ -25578,10 +25581,10 @@
         <v>142</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K61" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L61" s="44">
         <v>10</v>
@@ -25653,10 +25656,10 @@
         <v>55055</v>
       </c>
       <c r="AI61" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ61" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK61" s="44"/>
     </row>
@@ -25666,10 +25669,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_TropicalFish_International</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D62" s="46" t="s">
         <v>125</v>
@@ -25690,10 +25693,10 @@
         <v>142</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K62" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L62" s="44">
         <v>10</v>
@@ -25765,10 +25768,10 @@
         <v>55055</v>
       </c>
       <c r="AI62" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ62" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK62" s="44"/>
     </row>
@@ -25778,10 +25781,10 @@
         <v>createAndConfirmAdvanceBookingLiveAnimals_LIVE_HatchingEggs_International</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D63" s="46" t="s">
         <v>125</v>
@@ -25802,10 +25805,10 @@
         <v>142</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K63" s="44" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="L63" s="44">
         <v>10</v>
@@ -25877,10 +25880,10 @@
         <v>55055</v>
       </c>
       <c r="AI63" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ63" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK63" s="44"/>
     </row>
@@ -25890,7 +25893,7 @@
         <v>createAndConfirmGuidedBookingParcellessthan16OZ_STANDARD_NA_Domestic</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C64" s="49" t="s">
         <v>192</v>
@@ -25917,13 +25920,13 @@
         <v>35</v>
       </c>
       <c r="K64" s="49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L64" s="49">
         <v>10</v>
       </c>
       <c r="M64" s="49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N64" s="49">
         <v>1</v>
@@ -25938,7 +25941,7 @@
         <v>10</v>
       </c>
       <c r="R64" s="49" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S64" s="49" t="s">
         <v>19</v>
@@ -25992,7 +25995,7 @@
         <v>106</v>
       </c>
       <c r="AJ64" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65" spans="1:38">
@@ -26001,7 +26004,7 @@
         <v>createAndConfirmGuidedBookingParcellessthan16OZ_DSH_NA_Domestic</v>
       </c>
       <c r="B65" s="49" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C65" s="49" t="s">
         <v>113</v>
@@ -26028,13 +26031,13 @@
         <v>35</v>
       </c>
       <c r="K65" s="49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L65" s="49">
         <v>20</v>
       </c>
       <c r="M65" s="49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N65" s="49">
         <v>2</v>
@@ -26103,7 +26106,7 @@
         <v>106</v>
       </c>
       <c r="AJ65" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:38">
@@ -26112,7 +26115,7 @@
         <v>createAndConfirmGuidedBookingParcellessthan16OZ_DMD_NA_Domestic</v>
       </c>
       <c r="B66" s="49" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C66" s="49" t="s">
         <v>163</v>
@@ -26139,13 +26142,13 @@
         <v>35</v>
       </c>
       <c r="K66" s="49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L66" s="49">
         <v>40</v>
       </c>
       <c r="M66" s="49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N66" s="49">
         <v>4</v>
@@ -26160,7 +26163,7 @@
         <v>10</v>
       </c>
       <c r="R66" s="49" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S66" s="49" t="s">
         <v>19</v>
@@ -26214,7 +26217,7 @@
         <v>106</v>
       </c>
       <c r="AJ66" s="15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="67" spans="1:38">
@@ -26223,10 +26226,10 @@
         <v>createAndConfirmGuidedBookingParcellessthan16OZ_GENERAL_NA_International</v>
       </c>
       <c r="B67" s="49" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D67" s="46" t="s">
         <v>125</v>
@@ -26250,13 +26253,13 @@
         <v>35</v>
       </c>
       <c r="K67" s="49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L67" s="49">
         <v>10</v>
       </c>
       <c r="M67" s="49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N67" s="49">
         <v>1</v>
@@ -26322,10 +26325,10 @@
         <v>55055</v>
       </c>
       <c r="AI67" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ67" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:38">
@@ -26334,10 +26337,10 @@
         <v>createAndConfirmGuidedBookingParcellessthan16OZ_EXPRESS_NA_International</v>
       </c>
       <c r="B68" s="49" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C68" s="49" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D68" s="46" t="s">
         <v>125</v>
@@ -26355,19 +26358,19 @@
         <v>142</v>
       </c>
       <c r="I68" s="49" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J68" s="49" t="s">
         <v>35</v>
       </c>
       <c r="K68" s="49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L68" s="49">
         <v>40</v>
       </c>
       <c r="M68" s="49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N68" s="49">
         <v>3</v>
@@ -26382,7 +26385,7 @@
         <v>10</v>
       </c>
       <c r="R68" s="49" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S68" s="49" t="s">
         <v>19</v>
@@ -26433,10 +26436,10 @@
         <v>55055</v>
       </c>
       <c r="AI68" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ68" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:38">
@@ -26445,10 +26448,10 @@
         <v>createAndConfirmGuidedBookingParcellessthan16OZ_CRITICAL_NA_International</v>
       </c>
       <c r="B69" s="49" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C69" s="49" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D69" s="46" t="s">
         <v>125</v>
@@ -26466,19 +26469,19 @@
         <v>142</v>
       </c>
       <c r="I69" s="49" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J69" s="49" t="s">
         <v>35</v>
       </c>
       <c r="K69" s="49" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L69" s="49">
         <v>90</v>
       </c>
       <c r="M69" s="49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="N69" s="49">
         <v>4</v>
@@ -26544,10 +26547,10 @@
         <v>55055</v>
       </c>
       <c r="AI69" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ69" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:38" s="50" customFormat="1">
@@ -26556,7 +26559,7 @@
         <v>createAndConfirmGuidedBookingParcels_STANDARD_NA_Domestic</v>
       </c>
       <c r="B70" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C70" s="50" t="s">
         <v>192</v>
@@ -26583,13 +26586,13 @@
         <v>35</v>
       </c>
       <c r="K70" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L70" s="50">
         <v>30</v>
       </c>
       <c r="M70" s="50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N70" s="50">
         <v>1</v>
@@ -26604,7 +26607,7 @@
         <v>10</v>
       </c>
       <c r="R70" s="50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S70" s="50" t="s">
         <v>35</v>
@@ -26658,7 +26661,7 @@
         <v>106</v>
       </c>
       <c r="AJ70" s="51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AL70" s="50">
         <v>2</v>
@@ -26670,7 +26673,7 @@
         <v>createAndConfirmGuidedBookingParcels_DSH_NA_Domestic</v>
       </c>
       <c r="B71" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C71" s="50" t="s">
         <v>113</v>
@@ -26688,16 +26691,16 @@
         <v>35</v>
       </c>
       <c r="H71" s="50" t="s">
+        <v>231</v>
+      </c>
+      <c r="I71" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="I71" s="50" t="s">
-        <v>233</v>
-      </c>
       <c r="J71" s="50" t="s">
         <v>35</v>
       </c>
       <c r="K71" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L71" s="50">
         <v>60</v>
@@ -26772,7 +26775,7 @@
         <v>106</v>
       </c>
       <c r="AJ71" s="51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AL71" s="50">
         <v>3</v>
@@ -26784,7 +26787,7 @@
         <v>createAndConfirmGuidedBookingParcels_DMD_NA_Domestic</v>
       </c>
       <c r="B72" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C72" s="50" t="s">
         <v>163</v>
@@ -26811,13 +26814,13 @@
         <v>35</v>
       </c>
       <c r="K72" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L72" s="50">
         <v>90</v>
       </c>
       <c r="M72" s="50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N72" s="50">
         <v>4</v>
@@ -26832,7 +26835,7 @@
         <v>10</v>
       </c>
       <c r="R72" s="50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S72" s="50" t="s">
         <v>35</v>
@@ -26886,7 +26889,7 @@
         <v>106</v>
       </c>
       <c r="AJ72" s="51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AL72" s="50">
         <v>4</v>
@@ -26898,10 +26901,10 @@
         <v>createAndConfirmGuidedBookingParcels_GENERAL_NA_International</v>
       </c>
       <c r="B73" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="C73" s="50" t="s">
         <v>234</v>
-      </c>
-      <c r="C73" s="50" t="s">
-        <v>235</v>
       </c>
       <c r="D73" s="46" t="s">
         <v>125</v>
@@ -26919,13 +26922,13 @@
         <v>142</v>
       </c>
       <c r="I73" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J73" s="50" t="s">
         <v>35</v>
       </c>
       <c r="K73" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L73" s="50">
         <v>30</v>
@@ -26997,10 +27000,10 @@
         <v>55055</v>
       </c>
       <c r="AI73" s="51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ73" s="51" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL73" s="50">
         <v>5</v>
@@ -27012,10 +27015,10 @@
         <v>createAndConfirmGuidedBookingParcels_EXPRESS_HEAVY_NA_International</v>
       </c>
       <c r="B74" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D74" s="46" t="s">
         <v>125</v>
@@ -27033,19 +27036,19 @@
         <v>142</v>
       </c>
       <c r="I74" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J74" s="50" t="s">
         <v>35</v>
       </c>
       <c r="K74" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L74" s="50">
         <v>60</v>
       </c>
       <c r="M74" s="50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N74" s="50">
         <v>1</v>
@@ -27060,7 +27063,7 @@
         <v>10</v>
       </c>
       <c r="R74" s="50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S74" s="50" t="s">
         <v>35</v>
@@ -27111,10 +27114,10 @@
         <v>55055</v>
       </c>
       <c r="AI74" s="51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ74" s="51" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL74" s="50">
         <v>6</v>
@@ -27126,10 +27129,10 @@
         <v>createAndConfirmGuidedBookingParcels_CRITICAL_HEAVY_NA_International</v>
       </c>
       <c r="B75" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C75" s="50" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D75" s="46" t="s">
         <v>125</v>
@@ -27147,13 +27150,13 @@
         <v>142</v>
       </c>
       <c r="I75" s="50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J75" s="50" t="s">
         <v>35</v>
       </c>
       <c r="K75" s="50" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L75" s="50">
         <v>100</v>
@@ -27225,10 +27228,10 @@
         <v>55055</v>
       </c>
       <c r="AI75" s="51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ75" s="51" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AL75" s="50">
         <v>7</v>
@@ -27240,10 +27243,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_LIVE_Bird_Domestic</v>
       </c>
       <c r="B76" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C76" s="52" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D76" s="46" t="s">
         <v>125</v>
@@ -27264,16 +27267,16 @@
         <v>165</v>
       </c>
       <c r="J76" s="52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K76" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L76" s="52">
         <v>10</v>
       </c>
       <c r="M76" s="52" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N76" s="52">
         <v>1</v>
@@ -27288,7 +27291,7 @@
         <v>10</v>
       </c>
       <c r="R76" s="52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S76" s="52" t="s">
         <v>19</v>
@@ -27342,7 +27345,7 @@
         <v>106</v>
       </c>
       <c r="AJ76" s="53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" spans="1:38" s="52" customFormat="1">
@@ -27351,10 +27354,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_LIVE_Cat_Domestic</v>
       </c>
       <c r="B77" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C77" s="52" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D77" s="46" t="s">
         <v>125</v>
@@ -27378,7 +27381,7 @@
         <v>39</v>
       </c>
       <c r="K77" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L77" s="52">
         <v>20</v>
@@ -27453,7 +27456,7 @@
         <v>106</v>
       </c>
       <c r="AJ77" s="53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="78" spans="1:38" s="52" customFormat="1">
@@ -27462,10 +27465,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_LIVE_ColdBloodedAnimal_Domestic</v>
       </c>
       <c r="B78" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C78" s="52" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D78" s="46" t="s">
         <v>125</v>
@@ -27486,16 +27489,16 @@
         <v>165</v>
       </c>
       <c r="J78" s="52" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K78" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L78" s="52">
         <v>30</v>
       </c>
       <c r="M78" s="52" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N78" s="52">
         <v>1</v>
@@ -27510,7 +27513,7 @@
         <v>10</v>
       </c>
       <c r="R78" s="52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S78" s="52" t="s">
         <v>19</v>
@@ -27564,7 +27567,7 @@
         <v>106</v>
       </c>
       <c r="AJ78" s="53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:38" s="52" customFormat="1">
@@ -27573,10 +27576,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_LIVE_Dog_Domestic</v>
       </c>
       <c r="B79" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C79" s="52" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D79" s="46" t="s">
         <v>125</v>
@@ -27597,10 +27600,10 @@
         <v>165</v>
       </c>
       <c r="J79" s="52" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K79" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L79" s="52">
         <v>40</v>
@@ -27675,7 +27678,7 @@
         <v>106</v>
       </c>
       <c r="AJ79" s="53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:38" s="52" customFormat="1">
@@ -27684,10 +27687,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_LIVE_HatchingEggs_Domestic</v>
       </c>
       <c r="B80" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="52" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D80" s="46" t="s">
         <v>125</v>
@@ -27708,16 +27711,16 @@
         <v>165</v>
       </c>
       <c r="J80" s="52" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K80" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L80" s="52">
         <v>10</v>
       </c>
       <c r="M80" s="52" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N80" s="52">
         <v>1</v>
@@ -27732,7 +27735,7 @@
         <v>10</v>
       </c>
       <c r="R80" s="52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S80" s="52" t="s">
         <v>19</v>
@@ -27786,7 +27789,7 @@
         <v>106</v>
       </c>
       <c r="AJ80" s="53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="81" spans="1:36" s="52" customFormat="1">
@@ -27795,10 +27798,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_LIVE_WarmBloodedAnimal_Domestic</v>
       </c>
       <c r="B81" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C81" s="52" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D81" s="46" t="s">
         <v>125</v>
@@ -27816,13 +27819,13 @@
         <v>142</v>
       </c>
       <c r="I81" s="52" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J81" s="52" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K81" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L81" s="52">
         <v>40</v>
@@ -27897,7 +27900,7 @@
         <v>106</v>
       </c>
       <c r="AJ81" s="53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="82" spans="1:36" s="52" customFormat="1">
@@ -27906,10 +27909,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_SPECIALIZED_LIVE_Bird_International</v>
       </c>
       <c r="B82" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C82" s="52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D82" s="46" t="s">
         <v>125</v>
@@ -27930,16 +27933,16 @@
         <v>165</v>
       </c>
       <c r="J82" s="52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K82" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L82" s="52">
         <v>10</v>
       </c>
       <c r="M82" s="52" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N82" s="52">
         <v>1</v>
@@ -27954,7 +27957,7 @@
         <v>10</v>
       </c>
       <c r="R82" s="52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S82" s="52" t="s">
         <v>19</v>
@@ -28005,10 +28008,10 @@
         <v>55055</v>
       </c>
       <c r="AI82" s="53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ82" s="53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="1:36" s="52" customFormat="1">
@@ -28017,10 +28020,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_SPECIALIZED_LIVE_Cat_International</v>
       </c>
       <c r="B83" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C83" s="52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D83" s="46" t="s">
         <v>125</v>
@@ -28044,7 +28047,7 @@
         <v>39</v>
       </c>
       <c r="K83" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L83" s="52">
         <v>30</v>
@@ -28116,10 +28119,10 @@
         <v>55055</v>
       </c>
       <c r="AI83" s="53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ83" s="53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:36" s="52" customFormat="1">
@@ -28128,10 +28131,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_SPECIALIZED_LIVE_ColdBloodedAnimal_International</v>
       </c>
       <c r="B84" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C84" s="52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D84" s="46" t="s">
         <v>125</v>
@@ -28152,16 +28155,16 @@
         <v>165</v>
       </c>
       <c r="J84" s="52" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K84" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L84" s="52">
         <v>60</v>
       </c>
       <c r="M84" s="52" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N84" s="52">
         <v>1</v>
@@ -28176,7 +28179,7 @@
         <v>10</v>
       </c>
       <c r="R84" s="52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S84" s="52" t="s">
         <v>19</v>
@@ -28227,10 +28230,10 @@
         <v>55055</v>
       </c>
       <c r="AI84" s="53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ84" s="53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:36" s="52" customFormat="1">
@@ -28239,10 +28242,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_SPECIALIZED_LIVE_Dog_International</v>
       </c>
       <c r="B85" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C85" s="52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D85" s="46" t="s">
         <v>125</v>
@@ -28263,10 +28266,10 @@
         <v>165</v>
       </c>
       <c r="J85" s="52" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K85" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L85" s="52">
         <v>20</v>
@@ -28338,10 +28341,10 @@
         <v>55055</v>
       </c>
       <c r="AI85" s="53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ85" s="53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="86" spans="1:36" s="52" customFormat="1">
@@ -28350,10 +28353,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_SPECIALIZED_LIVE_HatchingEggs_International</v>
       </c>
       <c r="B86" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D86" s="46" t="s">
         <v>125</v>
@@ -28374,16 +28377,16 @@
         <v>165</v>
       </c>
       <c r="J86" s="52" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K86" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L86" s="52">
         <v>10</v>
       </c>
       <c r="M86" s="52" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N86" s="52">
         <v>1</v>
@@ -28398,7 +28401,7 @@
         <v>10</v>
       </c>
       <c r="R86" s="52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S86" s="52" t="s">
         <v>19</v>
@@ -28449,10 +28452,10 @@
         <v>55055</v>
       </c>
       <c r="AI86" s="53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ86" s="53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="87" spans="1:36" s="52" customFormat="1">
@@ -28461,10 +28464,10 @@
         <v>createAndConfirmGuidedBookingPetsandLive_SPECIALIZED_LIVE_WarmBloodedAnimal_International</v>
       </c>
       <c r="B87" s="52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C87" s="52" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D87" s="46" t="s">
         <v>125</v>
@@ -28485,10 +28488,10 @@
         <v>165</v>
       </c>
       <c r="J87" s="52" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K87" s="52" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L87" s="52">
         <v>90</v>
@@ -28560,10 +28563,10 @@
         <v>55055</v>
       </c>
       <c r="AI87" s="53" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ87" s="53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="88" spans="1:36" s="1" customFormat="1">
@@ -28599,13 +28602,13 @@
         <v>57</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L88" s="1">
         <v>11</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N88" s="1">
         <v>1</v>
@@ -28620,7 +28623,7 @@
         <v>10</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S88" s="1" t="s">
         <v>35</v>
@@ -28641,7 +28644,7 @@
         <v>20</v>
       </c>
       <c r="Y88" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Z88" s="47" t="s">
         <v>23</v>
@@ -28674,7 +28677,7 @@
         <v>106</v>
       </c>
       <c r="AJ88" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="89" spans="1:36" s="1" customFormat="1">
@@ -28710,7 +28713,7 @@
         <v>115</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L89" s="1">
         <v>12</v>
@@ -28785,7 +28788,7 @@
         <v>106</v>
       </c>
       <c r="AJ89" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:36" s="1" customFormat="1">
@@ -28821,13 +28824,13 @@
         <v>116</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L90" s="1">
         <v>13</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N90" s="1">
         <v>1</v>
@@ -28842,7 +28845,7 @@
         <v>10</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S90" s="1" t="s">
         <v>19</v>
@@ -28896,7 +28899,7 @@
         <v>106</v>
       </c>
       <c r="AJ90" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="91" spans="1:36" s="1" customFormat="1">
@@ -28932,7 +28935,7 @@
         <v>69</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L91" s="1">
         <v>14</v>
@@ -29007,7 +29010,7 @@
         <v>106</v>
       </c>
       <c r="AJ91" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:36" s="1" customFormat="1">
@@ -29043,13 +29046,13 @@
         <v>117</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L92" s="1">
         <v>15</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N92" s="1">
         <v>1</v>
@@ -29064,7 +29067,7 @@
         <v>10</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S92" s="1" t="s">
         <v>19</v>
@@ -29118,7 +29121,7 @@
         <v>106</v>
       </c>
       <c r="AJ92" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:36" s="1" customFormat="1">
@@ -29148,13 +29151,13 @@
         <v>142</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>57</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L93" s="1">
         <v>10</v>
@@ -29196,7 +29199,7 @@
         <v>20</v>
       </c>
       <c r="Y93" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Z93" s="47" t="s">
         <v>23</v>
@@ -29226,10 +29229,10 @@
         <v>55055</v>
       </c>
       <c r="AI93" s="54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ93" s="54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:36" s="1" customFormat="1">
@@ -29259,19 +29262,19 @@
         <v>142</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>115</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L94" s="1">
         <v>11</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N94" s="1">
         <v>1</v>
@@ -29286,7 +29289,7 @@
         <v>10</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S94" s="1" t="s">
         <v>19</v>
@@ -29337,10 +29340,10 @@
         <v>55055</v>
       </c>
       <c r="AI94" s="54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ94" s="54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:36" s="1" customFormat="1">
@@ -29352,7 +29355,7 @@
         <v>27</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D95" s="46" t="s">
         <v>125</v>
@@ -29370,13 +29373,13 @@
         <v>142</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>116</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L95" s="1">
         <v>12</v>
@@ -29448,10 +29451,10 @@
         <v>55055</v>
       </c>
       <c r="AI95" s="54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ95" s="54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:36" s="1" customFormat="1">
@@ -29463,7 +29466,7 @@
         <v>27</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D96" s="46" t="s">
         <v>125</v>
@@ -29481,19 +29484,19 @@
         <v>142</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>69</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L96" s="1">
         <v>130</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N96" s="1">
         <v>1</v>
@@ -29508,7 +29511,7 @@
         <v>10</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S96" s="1" t="s">
         <v>19</v>
@@ -29559,10 +29562,10 @@
         <v>55055</v>
       </c>
       <c r="AI96" s="54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ96" s="54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:36" s="1" customFormat="1">
@@ -29574,7 +29577,7 @@
         <v>27</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D97" s="46" t="s">
         <v>125</v>
@@ -29592,19 +29595,19 @@
         <v>142</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>117</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L97" s="1">
         <v>130</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N97" s="1">
         <v>1</v>
@@ -29670,10 +29673,10 @@
         <v>55055</v>
       </c>
       <c r="AI97" s="54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ97" s="54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:36" s="55" customFormat="1">
@@ -29700,22 +29703,22 @@
         <v>35</v>
       </c>
       <c r="H98" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="I98" s="55" t="s">
         <v>252</v>
-      </c>
-      <c r="I98" s="55" t="s">
-        <v>253</v>
       </c>
       <c r="J98" s="55" t="s">
         <v>54</v>
       </c>
       <c r="K98" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L98" s="55">
         <v>11</v>
       </c>
       <c r="M98" s="55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N98" s="55">
         <v>1</v>
@@ -29751,7 +29754,7 @@
         <v>20</v>
       </c>
       <c r="Y98" s="55" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Z98" s="47" t="s">
         <v>23</v>
@@ -29784,7 +29787,7 @@
         <v>106</v>
       </c>
       <c r="AJ98" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="99" spans="1:36" s="55" customFormat="1">
@@ -29814,13 +29817,13 @@
         <v>164</v>
       </c>
       <c r="I99" s="55" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J99" s="55" t="s">
         <v>175</v>
       </c>
       <c r="K99" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L99" s="55">
         <v>12</v>
@@ -29862,7 +29865,7 @@
         <v>20</v>
       </c>
       <c r="Y99" s="55" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Z99" s="47" t="s">
         <v>23</v>
@@ -29895,7 +29898,7 @@
         <v>106</v>
       </c>
       <c r="AJ99" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="100" spans="1:36" s="55" customFormat="1">
@@ -29922,22 +29925,22 @@
         <v>35</v>
       </c>
       <c r="H100" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="I100" s="55" t="s">
         <v>232</v>
-      </c>
-      <c r="I100" s="55" t="s">
-        <v>233</v>
       </c>
       <c r="J100" s="55" t="s">
         <v>63</v>
       </c>
       <c r="K100" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L100" s="55">
         <v>55</v>
       </c>
       <c r="M100" s="55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N100" s="55">
         <v>2</v>
@@ -29952,7 +29955,7 @@
         <v>10</v>
       </c>
       <c r="R100" s="55" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S100" s="55" t="s">
         <v>35</v>
@@ -30006,7 +30009,7 @@
         <v>106</v>
       </c>
       <c r="AJ100" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:36" s="55" customFormat="1">
@@ -30033,7 +30036,7 @@
         <v>35</v>
       </c>
       <c r="H101" s="55" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I101" s="55" t="s">
         <v>143</v>
@@ -30042,7 +30045,7 @@
         <v>193</v>
       </c>
       <c r="K101" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L101" s="55">
         <v>75</v>
@@ -30117,7 +30120,7 @@
         <v>106</v>
       </c>
       <c r="AJ101" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="102" spans="1:36" s="55" customFormat="1">
@@ -30153,13 +30156,13 @@
         <v>194</v>
       </c>
       <c r="K102" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L102" s="55">
         <v>115</v>
       </c>
       <c r="M102" s="55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N102" s="55">
         <v>4</v>
@@ -30174,7 +30177,7 @@
         <v>18</v>
       </c>
       <c r="R102" s="55" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S102" s="55" t="s">
         <v>35</v>
@@ -30228,7 +30231,7 @@
         <v>106</v>
       </c>
       <c r="AJ102" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103" spans="1:36" s="55" customFormat="1">
@@ -30258,13 +30261,13 @@
         <v>142</v>
       </c>
       <c r="I103" s="55" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J103" s="55" t="s">
         <v>54</v>
       </c>
       <c r="K103" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L103" s="55">
         <v>10</v>
@@ -30336,10 +30339,10 @@
         <v>55055</v>
       </c>
       <c r="AI103" s="56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ103" s="56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:36" s="55" customFormat="1">
@@ -30369,19 +30372,19 @@
         <v>142</v>
       </c>
       <c r="I104" s="55" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J104" s="55" t="s">
         <v>175</v>
       </c>
       <c r="K104" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L104" s="55">
         <v>11</v>
       </c>
       <c r="M104" s="55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N104" s="55">
         <v>1</v>
@@ -30447,10 +30450,10 @@
         <v>55055</v>
       </c>
       <c r="AI104" s="56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ104" s="56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" spans="1:36" s="55" customFormat="1">
@@ -30480,13 +30483,13 @@
         <v>142</v>
       </c>
       <c r="I105" s="55" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J105" s="55" t="s">
         <v>63</v>
       </c>
       <c r="K105" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L105" s="55">
         <v>12</v>
@@ -30558,10 +30561,10 @@
         <v>55055</v>
       </c>
       <c r="AI105" s="56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ105" s="56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="106" spans="1:36" s="55" customFormat="1">
@@ -30591,19 +30594,19 @@
         <v>142</v>
       </c>
       <c r="I106" s="55" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J106" s="55" t="s">
         <v>193</v>
       </c>
       <c r="K106" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L106" s="55">
         <v>13</v>
       </c>
       <c r="M106" s="55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N106" s="55">
         <v>1</v>
@@ -30618,7 +30621,7 @@
         <v>10</v>
       </c>
       <c r="R106" s="55" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S106" s="55" t="s">
         <v>35</v>
@@ -30669,10 +30672,10 @@
         <v>55055</v>
       </c>
       <c r="AI106" s="56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ106" s="56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:36" s="55" customFormat="1">
@@ -30702,13 +30705,13 @@
         <v>142</v>
       </c>
       <c r="I107" s="55" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J107" s="55" t="s">
         <v>194</v>
       </c>
       <c r="K107" s="55" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L107" s="55">
         <v>14</v>
@@ -30783,7 +30786,7 @@
         <v>106</v>
       </c>
       <c r="AJ107" s="56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="108" spans="1:36" s="57" customFormat="1">
@@ -30819,13 +30822,13 @@
         <v>177</v>
       </c>
       <c r="K108" s="57" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L108" s="57">
         <v>30</v>
       </c>
       <c r="M108" s="57" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N108" s="57">
         <v>1</v>
@@ -30840,7 +30843,7 @@
         <v>10</v>
       </c>
       <c r="R108" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S108" s="57" t="s">
         <v>19</v>
@@ -30894,7 +30897,7 @@
         <v>106</v>
       </c>
       <c r="AJ108" s="58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="109" spans="1:36" s="57" customFormat="1">
@@ -30921,7 +30924,7 @@
         <v>35</v>
       </c>
       <c r="H109" s="57" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I109" s="57" t="s">
         <v>143</v>
@@ -30930,7 +30933,7 @@
         <v>178</v>
       </c>
       <c r="K109" s="57" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L109" s="57">
         <v>50</v>
@@ -30954,7 +30957,7 @@
         <v>152</v>
       </c>
       <c r="S109" s="57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T109" s="57" t="s">
         <v>20</v>
@@ -31005,7 +31008,7 @@
         <v>106</v>
       </c>
       <c r="AJ109" s="58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="110" spans="1:36" s="57" customFormat="1">
@@ -31035,19 +31038,19 @@
         <v>165</v>
       </c>
       <c r="I110" s="57" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J110" s="57" t="s">
         <v>179</v>
       </c>
       <c r="K110" s="57" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L110" s="57">
         <v>60</v>
       </c>
       <c r="M110" s="57" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N110" s="57">
         <v>1</v>
@@ -31062,7 +31065,7 @@
         <v>10</v>
       </c>
       <c r="R110" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S110" s="57" t="s">
         <v>19</v>
@@ -31116,7 +31119,7 @@
         <v>106</v>
       </c>
       <c r="AJ110" s="58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="111" spans="1:36" s="57" customFormat="1">
@@ -31143,7 +31146,7 @@
         <v>35</v>
       </c>
       <c r="H111" s="57" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I111" s="57" t="s">
         <v>165</v>
@@ -31152,7 +31155,7 @@
         <v>180</v>
       </c>
       <c r="K111" s="57" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L111" s="57">
         <v>40</v>
@@ -31176,7 +31179,7 @@
         <v>152</v>
       </c>
       <c r="S111" s="57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T111" s="57" t="s">
         <v>20</v>
@@ -31227,7 +31230,7 @@
         <v>106</v>
       </c>
       <c r="AJ111" s="58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="112" spans="1:36" s="57" customFormat="1">
@@ -31263,13 +31266,13 @@
         <v>181</v>
       </c>
       <c r="K112" s="57" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L112" s="57">
         <v>50</v>
       </c>
       <c r="M112" s="57" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N112" s="57">
         <v>1</v>
@@ -31284,7 +31287,7 @@
         <v>10</v>
       </c>
       <c r="R112" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S112" s="57" t="s">
         <v>19</v>
@@ -31338,7 +31341,7 @@
         <v>106</v>
       </c>
       <c r="AJ112" s="58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="113" spans="1:36" s="72" customFormat="1">
@@ -31368,13 +31371,13 @@
         <v>142</v>
       </c>
       <c r="I113" s="72" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J113" s="72" t="s">
         <v>182</v>
       </c>
       <c r="K113" s="72" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L113" s="72">
         <v>60</v>
@@ -31398,7 +31401,7 @@
         <v>152</v>
       </c>
       <c r="S113" s="72" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T113" s="72" t="s">
         <v>20</v>
@@ -31446,10 +31449,10 @@
         <v>55055</v>
       </c>
       <c r="AI113" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ113" s="73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="114" spans="1:36" s="72" customFormat="1">
@@ -31461,7 +31464,7 @@
         <v>44</v>
       </c>
       <c r="C114" s="72" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D114" s="46" t="s">
         <v>125</v>
@@ -31479,19 +31482,19 @@
         <v>142</v>
       </c>
       <c r="I114" s="72" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J114" s="72" t="s">
         <v>177</v>
       </c>
       <c r="K114" s="72" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L114" s="72">
         <v>55</v>
       </c>
       <c r="M114" s="72" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N114" s="72">
         <v>1</v>
@@ -31506,7 +31509,7 @@
         <v>10</v>
       </c>
       <c r="R114" s="72" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S114" s="72" t="s">
         <v>19</v>
@@ -31557,10 +31560,10 @@
         <v>55055</v>
       </c>
       <c r="AI114" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ114" s="73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="115" spans="1:36" s="72" customFormat="1">
@@ -31572,7 +31575,7 @@
         <v>44</v>
       </c>
       <c r="C115" s="72" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D115" s="46" t="s">
         <v>125</v>
@@ -31590,13 +31593,13 @@
         <v>142</v>
       </c>
       <c r="I115" s="72" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J115" s="72" t="s">
         <v>178</v>
       </c>
       <c r="K115" s="72" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L115" s="72">
         <v>65</v>
@@ -31620,7 +31623,7 @@
         <v>152</v>
       </c>
       <c r="S115" s="72" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T115" s="72" t="s">
         <v>20</v>
@@ -31668,10 +31671,10 @@
         <v>55055</v>
       </c>
       <c r="AI115" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ115" s="73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:36" s="72" customFormat="1">
@@ -31683,7 +31686,7 @@
         <v>44</v>
       </c>
       <c r="C116" s="72" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D116" s="46" t="s">
         <v>125</v>
@@ -31701,19 +31704,19 @@
         <v>142</v>
       </c>
       <c r="I116" s="72" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J116" s="72" t="s">
         <v>179</v>
       </c>
       <c r="K116" s="72" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L116" s="72">
         <v>75</v>
       </c>
       <c r="M116" s="72" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N116" s="72">
         <v>1</v>
@@ -31728,7 +31731,7 @@
         <v>10</v>
       </c>
       <c r="R116" s="72" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S116" s="72" t="s">
         <v>19</v>
@@ -31779,10 +31782,10 @@
         <v>55055</v>
       </c>
       <c r="AI116" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ116" s="73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="117" spans="1:36" s="72" customFormat="1">
@@ -31794,7 +31797,7 @@
         <v>44</v>
       </c>
       <c r="C117" s="72" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D117" s="46" t="s">
         <v>125</v>
@@ -31812,13 +31815,13 @@
         <v>142</v>
       </c>
       <c r="I117" s="72" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J117" s="72" t="s">
         <v>180</v>
       </c>
       <c r="K117" s="72" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L117" s="72">
         <v>85</v>
@@ -31842,7 +31845,7 @@
         <v>152</v>
       </c>
       <c r="S117" s="72" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T117" s="72" t="s">
         <v>20</v>
@@ -31890,10 +31893,10 @@
         <v>55055</v>
       </c>
       <c r="AI117" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ117" s="73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118" spans="1:36" s="72" customFormat="1">
@@ -31905,7 +31908,7 @@
         <v>44</v>
       </c>
       <c r="C118" s="72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D118" s="46" t="s">
         <v>125</v>
@@ -31923,19 +31926,19 @@
         <v>142</v>
       </c>
       <c r="I118" s="72" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J118" s="72" t="s">
         <v>181</v>
       </c>
       <c r="K118" s="72" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L118" s="72">
         <v>65</v>
       </c>
       <c r="M118" s="72" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N118" s="72">
         <v>1</v>
@@ -31950,7 +31953,7 @@
         <v>10</v>
       </c>
       <c r="R118" s="72" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S118" s="72" t="s">
         <v>19</v>
@@ -32001,10 +32004,10 @@
         <v>55055</v>
       </c>
       <c r="AI118" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ118" s="73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="119" spans="1:36" s="72" customFormat="1">
@@ -32016,7 +32019,7 @@
         <v>44</v>
       </c>
       <c r="C119" s="72" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D119" s="46" t="s">
         <v>125</v>
@@ -32034,13 +32037,13 @@
         <v>142</v>
       </c>
       <c r="I119" s="72" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J119" s="72" t="s">
         <v>182</v>
       </c>
       <c r="K119" s="72" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L119" s="72">
         <v>45</v>
@@ -32064,7 +32067,7 @@
         <v>152</v>
       </c>
       <c r="S119" s="72" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T119" s="72" t="s">
         <v>20</v>
@@ -32112,10 +32115,10 @@
         <v>55055</v>
       </c>
       <c r="AI119" s="73" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ119" s="73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="120" spans="1:36" s="59" customFormat="1">
@@ -32151,13 +32154,13 @@
         <v>183</v>
       </c>
       <c r="K120" s="59" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L120" s="59">
         <v>30</v>
       </c>
       <c r="M120" s="59" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N120" s="59">
         <v>2</v>
@@ -32172,7 +32175,7 @@
         <v>10</v>
       </c>
       <c r="R120" s="59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S120" s="59" t="s">
         <v>35</v>
@@ -32226,7 +32229,7 @@
         <v>106</v>
       </c>
       <c r="AJ120" s="60" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="121" spans="1:36" s="59" customFormat="1">
@@ -32253,7 +32256,7 @@
         <v>35</v>
       </c>
       <c r="H121" s="59" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I121" s="59" t="s">
         <v>143</v>
@@ -32262,7 +32265,7 @@
         <v>184</v>
       </c>
       <c r="K121" s="59" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L121" s="59">
         <v>20</v>
@@ -32337,7 +32340,7 @@
         <v>106</v>
       </c>
       <c r="AJ121" s="60" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="122" spans="1:36" s="59" customFormat="1">
@@ -32367,19 +32370,19 @@
         <v>142</v>
       </c>
       <c r="I122" s="59" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J122" s="59" t="s">
         <v>183</v>
       </c>
       <c r="K122" s="59" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L122" s="59">
         <v>50</v>
       </c>
       <c r="M122" s="59" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N122" s="59">
         <v>4</v>
@@ -32394,7 +32397,7 @@
         <v>10</v>
       </c>
       <c r="R122" s="59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S122" s="59" t="s">
         <v>35</v>
@@ -32445,10 +32448,10 @@
         <v>55055</v>
       </c>
       <c r="AI122" s="60" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ122" s="60" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="123" spans="1:36" s="59" customFormat="1">
@@ -32478,13 +32481,13 @@
         <v>142</v>
       </c>
       <c r="I123" s="59" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J123" s="59" t="s">
         <v>184</v>
       </c>
       <c r="K123" s="59" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L123" s="59">
         <v>40</v>
@@ -32556,22 +32559,22 @@
         <v>55055</v>
       </c>
       <c r="AI123" s="60" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ123" s="60" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="124" spans="1:36" s="61" customFormat="1">
       <c r="A124" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_Domestic</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_Domestic</v>
       </c>
       <c r="B124" s="61" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C124" s="61" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D124" s="46" t="s">
         <v>125</v>
@@ -32595,7 +32598,7 @@
         <v>186</v>
       </c>
       <c r="K124" s="61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L124" s="61">
         <v>79</v>
@@ -32637,7 +32640,7 @@
         <v>20</v>
       </c>
       <c r="Y124" s="61" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Z124" s="47" t="s">
         <v>23</v>
@@ -32670,19 +32673,19 @@
         <v>106</v>
       </c>
       <c r="AJ124" s="62" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="125" spans="1:36" s="61" customFormat="1">
       <c r="A125" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_Domestic</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_Domestic</v>
       </c>
       <c r="B125" s="61" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C125" s="61" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D125" s="46" t="s">
         <v>125</v>
@@ -32706,10 +32709,10 @@
         <v>187</v>
       </c>
       <c r="K125" s="61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L125" s="61">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M125" s="61" t="s">
         <v>145</v>
@@ -32748,7 +32751,7 @@
         <v>20</v>
       </c>
       <c r="Y125" s="61" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z125" s="47" t="s">
         <v>23</v>
@@ -32781,19 +32784,19 @@
         <v>106</v>
       </c>
       <c r="AJ125" s="62" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="126" spans="1:36" s="61" customFormat="1">
       <c r="A126" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_Domestic</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_Domestic</v>
       </c>
       <c r="B126" s="61" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C126" s="61" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D126" s="46" t="s">
         <v>125</v>
@@ -32817,7 +32820,7 @@
         <v>188</v>
       </c>
       <c r="K126" s="61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L126" s="61">
         <v>59</v>
@@ -32859,7 +32862,7 @@
         <v>20</v>
       </c>
       <c r="Y126" s="61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Z126" s="47" t="s">
         <v>23</v>
@@ -32892,19 +32895,19 @@
         <v>106</v>
       </c>
       <c r="AJ126" s="62" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="127" spans="1:36" s="61" customFormat="1">
       <c r="A127" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_International</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_International</v>
       </c>
       <c r="B127" s="61" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C127" s="61" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D127" s="46" t="s">
         <v>125</v>
@@ -32922,19 +32925,19 @@
         <v>142</v>
       </c>
       <c r="I127" s="61" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J127" s="61" t="s">
         <v>186</v>
       </c>
       <c r="K127" s="61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L127" s="61">
         <v>79</v>
       </c>
       <c r="M127" s="61" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N127" s="61">
         <v>1</v>
@@ -32949,7 +32952,7 @@
         <v>10</v>
       </c>
       <c r="R127" s="61" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S127" s="61" t="s">
         <v>35</v>
@@ -32970,7 +32973,7 @@
         <v>20</v>
       </c>
       <c r="Y127" s="61" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Z127" s="47" t="s">
         <v>23</v>
@@ -33000,22 +33003,22 @@
         <v>55055</v>
       </c>
       <c r="AI127" s="62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ127" s="62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="128" spans="1:36" s="61" customFormat="1">
       <c r="A128" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_International</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_International</v>
       </c>
       <c r="B128" s="61" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C128" s="61" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D128" s="46" t="s">
         <v>125</v>
@@ -33033,19 +33036,19 @@
         <v>142</v>
       </c>
       <c r="I128" s="61" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J128" s="61" t="s">
         <v>187</v>
       </c>
       <c r="K128" s="61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L128" s="61">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M128" s="61" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N128" s="61">
         <v>1</v>
@@ -33060,7 +33063,7 @@
         <v>10</v>
       </c>
       <c r="R128" s="61" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S128" s="61" t="s">
         <v>35</v>
@@ -33081,7 +33084,7 @@
         <v>20</v>
       </c>
       <c r="Y128" s="61" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z128" s="47" t="s">
         <v>23</v>
@@ -33111,22 +33114,22 @@
         <v>55055</v>
       </c>
       <c r="AI128" s="62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ128" s="62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="129" spans="1:36" s="61" customFormat="1">
       <c r="A129" s="61" t="str">
         <f t="shared" ref="A129" si="2">_xlfn.CONCAT("createAndConfirmGuidedBooking",SUBSTITUTE(B129," ","_"),"_",SUBSTITUTE(C129," ","_"),"_",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J129," ",""),"-",""),"/",""),"–",""),"+",""),"°",""),",",""),"_",SUBSTITUTE(AJ129," ","_"))</f>
-        <v>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_International</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_International</v>
       </c>
       <c r="B129" s="61" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C129" s="61" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="D129" s="46" t="s">
         <v>125</v>
@@ -33144,19 +33147,19 @@
         <v>142</v>
       </c>
       <c r="I129" s="61" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J129" s="61" t="s">
         <v>188</v>
       </c>
       <c r="K129" s="61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L129" s="61">
         <v>59</v>
       </c>
       <c r="M129" s="61" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N129" s="61">
         <v>1</v>
@@ -33171,7 +33174,7 @@
         <v>10</v>
       </c>
       <c r="R129" s="61" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="S129" s="61" t="s">
         <v>35</v>
@@ -33192,7 +33195,7 @@
         <v>20</v>
       </c>
       <c r="Y129" s="61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Z129" s="47" t="s">
         <v>23</v>
@@ -33222,10 +33225,10 @@
         <v>55055</v>
       </c>
       <c r="AI129" s="62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AJ129" s="62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -33442,7 +33445,7 @@
         <v>141</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L1" s="36" t="s">
         <v>196</v>
@@ -33520,7 +33523,7 @@
         <v>102</v>
       </c>
       <c r="AK1" s="36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL1" s="36" t="s">
         <v>73</v>
@@ -33537,7 +33540,7 @@
     </row>
     <row r="2" spans="1:41" ht="16.5" thickBot="1">
       <c r="A2" s="74" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B2" s="38" t="str" cm="1">
         <f t="array" ref="B2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -33579,7 +33582,7 @@
       </c>
       <c r="L2" s="38" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test General Cargo</v>
       </c>
       <c r="M2" s="38" cm="1">
         <f t="array" ref="M2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -33700,7 +33703,7 @@
     </row>
     <row r="3" spans="1:41" ht="16.5" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B3" s="38" t="str" cm="1">
         <f t="array" ref="B3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -33742,7 +33745,7 @@
       </c>
       <c r="L3" s="38" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test General Cargo</v>
       </c>
       <c r="M3" s="38" cm="1">
         <f t="array" ref="M3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -33863,7 +33866,7 @@
     </row>
     <row r="4" spans="1:41" ht="16.5" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B4" s="38" t="str" cm="1">
         <f t="array" ref="B4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -33906,7 +33909,7 @@
       </c>
       <c r="L4" s="38" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test General Cargo</v>
       </c>
       <c r="M4" s="38" cm="1">
         <f t="array" ref="M4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -34027,14 +34030,14 @@
     </row>
     <row r="5" spans="1:41" ht="16.5" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B5" s="38" t="str" cm="1">
         <f t="array" ref="B5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
         <v>General Cargo</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D5" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -34070,7 +34073,7 @@
       </c>
       <c r="L5" s="38" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test General Cargo</v>
       </c>
       <c r="M5" s="38" cm="1">
         <f t="array" ref="M5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -34191,14 +34194,14 @@
     </row>
     <row r="6" spans="1:41" ht="16.5" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B6" s="38" t="str" cm="1">
         <f t="array" ref="B6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
         <v>General Cargo</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D6" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -34234,7 +34237,7 @@
       </c>
       <c r="L6" s="38" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test General Cargo</v>
       </c>
       <c r="M6" s="38" cm="1">
         <f t="array" ref="M6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -34355,14 +34358,14 @@
     </row>
     <row r="7" spans="1:41" ht="16.5" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B7" s="38" t="str" cm="1">
         <f t="array" ref="B7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
         <v>General Cargo</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D7" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -34398,7 +34401,7 @@
       </c>
       <c r="L7" s="38" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test General Cargo</v>
       </c>
       <c r="M7" s="38" cm="1">
         <f t="array" ref="M7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -34601,7 +34604,7 @@
         <v>141</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L1" s="27" t="s">
         <v>196</v>
@@ -34679,7 +34682,7 @@
         <v>102</v>
       </c>
       <c r="AK1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL1" s="20" t="s">
         <v>73</v>
@@ -34687,7 +34690,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>47</v>
@@ -34729,7 +34732,7 @@
       </c>
       <c r="L2" s="31" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M2" s="29" cm="1">
         <f t="array" ref="M2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -34838,7 +34841,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>47</v>
@@ -34880,7 +34883,7 @@
       </c>
       <c r="L3" s="31" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M3" s="29" cm="1">
         <f t="array" ref="M3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -34989,7 +34992,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>47</v>
@@ -35031,7 +35034,7 @@
       </c>
       <c r="L4" s="31" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M4" s="29" cm="1">
         <f t="array" ref="M4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -35140,7 +35143,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>47</v>
@@ -35182,7 +35185,7 @@
       </c>
       <c r="L5" s="31" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M5" s="29" cm="1">
         <f t="array" ref="M5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -35291,7 +35294,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>47</v>
@@ -35333,7 +35336,7 @@
       </c>
       <c r="L6" s="31" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M6" s="29" cm="1">
         <f t="array" ref="M6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -35442,7 +35445,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>47</v>
@@ -35484,7 +35487,7 @@
       </c>
       <c r="L7" s="31" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M7" s="29" cm="1">
         <f t="array" ref="M7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -35593,7 +35596,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>47</v>
@@ -35635,7 +35638,7 @@
       </c>
       <c r="L8" s="31" t="str" cm="1">
         <f t="array" ref="L8">_xlfn.XLOOKUP($A8,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M8" s="29" cm="1">
         <f t="array" ref="M8">_xlfn.XLOOKUP($A8,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -35744,7 +35747,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>47</v>
@@ -35786,7 +35789,7 @@
       </c>
       <c r="L9" s="31" t="str" cm="1">
         <f t="array" ref="L9">_xlfn.XLOOKUP($A9,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M9" s="29" cm="1">
         <f t="array" ref="M9">_xlfn.XLOOKUP($A9,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -35895,7 +35898,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>47</v>
@@ -35937,7 +35940,7 @@
       </c>
       <c r="L10" s="31" t="str" cm="1">
         <f t="array" ref="L10">_xlfn.XLOOKUP($A10,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M10" s="29" cm="1">
         <f t="array" ref="M10">_xlfn.XLOOKUP($A10,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -36046,7 +36049,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>47</v>
@@ -36088,7 +36091,7 @@
       </c>
       <c r="L11" s="31" t="str" cm="1">
         <f t="array" ref="L11">_xlfn.XLOOKUP($A11,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Perishables</v>
       </c>
       <c r="M11" s="29" cm="1">
         <f t="array" ref="M11">_xlfn.XLOOKUP($A11,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -36255,7 +36258,7 @@
         <v>141</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L1" s="27" t="s">
         <v>196</v>
@@ -36333,7 +36336,7 @@
         <v>102</v>
       </c>
       <c r="AK1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL1" s="20" t="s">
         <v>73</v>
@@ -36341,7 +36344,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>58</v>
@@ -36383,7 +36386,7 @@
       </c>
       <c r="L2" s="31" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M2" s="31" cm="1">
         <f t="array" ref="M2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -36492,7 +36495,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>58</v>
@@ -36534,7 +36537,7 @@
       </c>
       <c r="L3" s="31" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M3" s="31" cm="1">
         <f t="array" ref="M3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -36643,7 +36646,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>58</v>
@@ -36685,7 +36688,7 @@
       </c>
       <c r="L4" s="31" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M4" s="31" cm="1">
         <f t="array" ref="M4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -36794,7 +36797,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>58</v>
@@ -36836,7 +36839,7 @@
       </c>
       <c r="L5" s="31" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M5" s="31" cm="1">
         <f t="array" ref="M5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -36945,7 +36948,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>58</v>
@@ -36987,7 +36990,7 @@
       </c>
       <c r="L6" s="31" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M6" s="31" cm="1">
         <f t="array" ref="M6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -37096,7 +37099,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>58</v>
@@ -37138,7 +37141,7 @@
       </c>
       <c r="L7" s="31" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M7" s="31" cm="1">
         <f t="array" ref="M7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -37247,7 +37250,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>58</v>
@@ -37289,7 +37292,7 @@
       </c>
       <c r="L8" s="31" t="str" cm="1">
         <f t="array" ref="L8">_xlfn.XLOOKUP($A8,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M8" s="31" cm="1">
         <f t="array" ref="M8">_xlfn.XLOOKUP($A8,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -37398,7 +37401,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>58</v>
@@ -37440,7 +37443,7 @@
       </c>
       <c r="L9" s="31" t="str" cm="1">
         <f t="array" ref="L9">_xlfn.XLOOKUP($A9,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M9" s="31" cm="1">
         <f t="array" ref="M9">_xlfn.XLOOKUP($A9,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -37549,7 +37552,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>58</v>
@@ -37591,7 +37594,7 @@
       </c>
       <c r="L10" s="31" t="str" cm="1">
         <f t="array" ref="L10">_xlfn.XLOOKUP($A10,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M10" s="31" cm="1">
         <f t="array" ref="M10">_xlfn.XLOOKUP($A10,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -37700,7 +37703,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>58</v>
@@ -37742,7 +37745,7 @@
       </c>
       <c r="L11" s="31" t="str" cm="1">
         <f t="array" ref="L11">_xlfn.XLOOKUP($A11,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Pharma</v>
       </c>
       <c r="M11" s="31" cm="1">
         <f t="array" ref="M11">_xlfn.XLOOKUP($A11,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -37907,7 +37910,7 @@
         <v>141</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L1" s="27" t="s">
         <v>196</v>
@@ -37985,7 +37988,7 @@
         <v>102</v>
       </c>
       <c r="AK1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL1" s="20" t="s">
         <v>73</v>
@@ -37993,7 +37996,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>44</v>
@@ -38035,7 +38038,7 @@
       </c>
       <c r="L2" s="31" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M2" s="31" cm="1">
         <f t="array" ref="M2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -38144,7 +38147,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>44</v>
@@ -38186,7 +38189,7 @@
       </c>
       <c r="L3" s="31" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M3" s="31" cm="1">
         <f t="array" ref="M3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -38295,7 +38298,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>44</v>
@@ -38337,7 +38340,7 @@
       </c>
       <c r="L4" s="31" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M4" s="31" cm="1">
         <f t="array" ref="M4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -38446,7 +38449,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>44</v>
@@ -38488,7 +38491,7 @@
       </c>
       <c r="L5" s="31" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M5" s="31" cm="1">
         <f t="array" ref="M5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -38597,7 +38600,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>44</v>
@@ -38639,7 +38642,7 @@
       </c>
       <c r="L6" s="31" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M6" s="31" cm="1">
         <f t="array" ref="M6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -38748,7 +38751,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>44</v>
@@ -38790,7 +38793,7 @@
       </c>
       <c r="L7" s="31" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M7" s="31" cm="1">
         <f t="array" ref="M7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -38899,7 +38902,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>44</v>
@@ -38941,7 +38944,7 @@
       </c>
       <c r="L8" s="31" t="str" cm="1">
         <f t="array" ref="L8">_xlfn.XLOOKUP($A8,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M8" s="31" cm="1">
         <f t="array" ref="M8">_xlfn.XLOOKUP($A8,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -39050,7 +39053,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>44</v>
@@ -39092,7 +39095,7 @@
       </c>
       <c r="L9" s="31" t="str" cm="1">
         <f t="array" ref="L9">_xlfn.XLOOKUP($A9,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M9" s="31" cm="1">
         <f t="array" ref="M9">_xlfn.XLOOKUP($A9,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -39201,7 +39204,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>44</v>
@@ -39243,7 +39246,7 @@
       </c>
       <c r="L10" s="31" t="str" cm="1">
         <f t="array" ref="L10">_xlfn.XLOOKUP($A10,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M10" s="31" cm="1">
         <f t="array" ref="M10">_xlfn.XLOOKUP($A10,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -39352,7 +39355,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>44</v>
@@ -39394,7 +39397,7 @@
       </c>
       <c r="L11" s="31" t="str" cm="1">
         <f t="array" ref="L11">_xlfn.XLOOKUP($A11,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M11" s="31" cm="1">
         <f t="array" ref="M11">_xlfn.XLOOKUP($A11,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -39503,7 +39506,7 @@
     </row>
     <row r="12" spans="1:38" ht="17" thickBot="1">
       <c r="A12" s="75" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>44</v>
@@ -39545,7 +39548,7 @@
       </c>
       <c r="L12" s="31" t="str" cm="1">
         <f t="array" ref="L12">_xlfn.XLOOKUP($A12,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M12" s="31" cm="1">
         <f t="array" ref="M12">_xlfn.XLOOKUP($A12,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -39654,7 +39657,7 @@
     </row>
     <row r="13" spans="1:38" ht="17" thickBot="1">
       <c r="A13" s="75" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>44</v>
@@ -39696,7 +39699,7 @@
       </c>
       <c r="L13" s="31" t="str" cm="1">
         <f t="array" ref="L13">_xlfn.XLOOKUP($A13,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Medical</v>
       </c>
       <c r="M13" s="31" cm="1">
         <f t="array" ref="M13">_xlfn.XLOOKUP($A13,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -39862,7 +39865,7 @@
         <v>141</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L1" s="27" t="s">
         <v>196</v>
@@ -39940,7 +39943,7 @@
         <v>102</v>
       </c>
       <c r="AK1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL1" s="20" t="s">
         <v>73</v>
@@ -39948,7 +39951,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>87</v>
@@ -39990,7 +39993,7 @@
       </c>
       <c r="L2" s="31" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Valuables</v>
       </c>
       <c r="M2" s="31" cm="1">
         <f t="array" ref="M2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -40099,7 +40102,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>87</v>
@@ -40141,7 +40144,7 @@
       </c>
       <c r="L3" s="31" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Valuables</v>
       </c>
       <c r="M3" s="31" cm="1">
         <f t="array" ref="M3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -40250,7 +40253,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>87</v>
@@ -40292,7 +40295,7 @@
       </c>
       <c r="L4" s="31" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Valuables</v>
       </c>
       <c r="M4" s="31" cm="1">
         <f t="array" ref="M4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -40401,7 +40404,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>87</v>
@@ -40443,7 +40446,7 @@
       </c>
       <c r="L5" s="31" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Valuables</v>
       </c>
       <c r="M5" s="31" cm="1">
         <f t="array" ref="M5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -40610,7 +40613,7 @@
         <v>141</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L1" s="27" t="s">
         <v>196</v>
@@ -40688,7 +40691,7 @@
         <v>102</v>
       </c>
       <c r="AK1" s="20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL1" s="20" t="s">
         <v>73</v>
@@ -40696,7 +40699,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>89</v>
@@ -40738,7 +40741,7 @@
       </c>
       <c r="L2" s="31" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Human Remains</v>
       </c>
       <c r="M2" s="31" cm="1">
         <f t="array" ref="M2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -40847,7 +40850,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>89</v>
@@ -40889,7 +40892,7 @@
       </c>
       <c r="L3" s="31" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Human Remains</v>
       </c>
       <c r="M3" s="31" cm="1">
         <f t="array" ref="M3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -40998,7 +41001,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>89</v>
@@ -41040,7 +41043,7 @@
       </c>
       <c r="L4" s="31" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Human Remains</v>
       </c>
       <c r="M4" s="31" cm="1">
         <f t="array" ref="M4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -41149,7 +41152,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>89</v>
@@ -41191,7 +41194,7 @@
       </c>
       <c r="L5" s="31" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Human Remains</v>
       </c>
       <c r="M5" s="31" cm="1">
         <f t="array" ref="M5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -41300,7 +41303,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>89</v>
@@ -41342,7 +41345,7 @@
       </c>
       <c r="L6" s="31" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Human Remains</v>
       </c>
       <c r="M6" s="31" cm="1">
         <f t="array" ref="M6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -41451,7 +41454,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>89</v>
@@ -41493,7 +41496,7 @@
       </c>
       <c r="L7" s="31" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(L$1,dataRowRange,ActualDataRange))</f>
-        <v>Test</v>
+        <v>Test Human Remains</v>
       </c>
       <c r="M7" s="31" cm="1">
         <f t="array" ref="M7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(M$1,dataRowRange,ActualDataRange))</f>
@@ -41610,6 +41613,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DFBCF867C5410147BDDAF2BCA37BA4E7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e24a40d5ebdbb3b92553f235188d50f6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2981db02-ca81-468a-9abd-70e82312b342" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db49c26ce236f576151feb411775a695" ns2:_="">
     <xsd:import namespace="2981db02-ca81-468a-9abd-70e82312b342"/>
@@ -41741,22 +41759,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C30B22D-1747-44FE-B15C-A00BE24DA1E1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="2981db02-ca81-468a-9abd-70e82312b342"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD641CF5-135D-42FC-A55D-82791A85B476}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED3BB4E-382D-479A-B77C-6CB5E1CFD30D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -41772,28 +41799,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD641CF5-135D-42FC-A55D-82791A85B476}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C30B22D-1747-44FE-B15C-A00BE24DA1E1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="2981db02-ca81-468a-9abd-70e82312b342"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
+++ b/CargoUIAutomationNew/src/test/resources/TestCasesMapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\p57448\Desktop\Cargo_B\Cargo\CargoUIAutomationNew\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130465E4-222D-4F23-AF9F-5549C932BCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A8BE43-9413-4083-9B71-24B7B62F9BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="2" xr2:uid="{1AB005B2-AFEC-3B46-93EF-50FA3BE3C5FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="13" activeTab="18" xr2:uid="{1AB005B2-AFEC-3B46-93EF-50FA3BE3C5FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Configuration" sheetId="14" r:id="rId1"/>
@@ -1096,27 +1096,6 @@
     <t>createAndConfirmGuidedBookingValuables_SAFE_Valuelessthan25000USD_International</t>
   </si>
   <si>
-    <t>CARE</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_Domestic</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_Domestic</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_Domestic</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_International</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_International</t>
-  </si>
-  <si>
-    <t>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_International</t>
-  </si>
-  <si>
     <t>createAndConfirmAdvanceBookingGeneral_Cargo_STANDARD_Loose_Domestic</t>
   </si>
   <si>
@@ -1308,14 +1287,42 @@
   <si>
     <t>Test Human Remains</t>
   </si>
+  <si>
+    <t>Cares</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_Domestic</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_Domestic</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_Domestic</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_International</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_International</t>
+  </si>
+  <si>
+    <t>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_International</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1635,9 +1642,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1645,25 +1652,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1671,25 +1678,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1699,14 +1706,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1715,45 +1722,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1762,7 +1769,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1813,21 +1820,21 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1836,11 +1843,14 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2370,7 +2380,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>209</v>
@@ -2521,7 +2531,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>209</v>
@@ -2672,7 +2682,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>209</v>
@@ -2823,7 +2833,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>209</v>
@@ -2974,7 +2984,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>209</v>
@@ -3125,7 +3135,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>209</v>
@@ -3276,7 +3286,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>209</v>
@@ -3427,7 +3437,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>209</v>
@@ -3578,7 +3588,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>209</v>
@@ -3729,7 +3739,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>209</v>
@@ -3880,7 +3890,7 @@
     </row>
     <row r="12" spans="1:38" ht="17" thickBot="1">
       <c r="A12" s="75" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>209</v>
@@ -4031,7 +4041,7 @@
     </row>
     <row r="13" spans="1:38" ht="17" thickBot="1">
       <c r="A13" s="75" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>209</v>
@@ -4182,7 +4192,7 @@
     </row>
     <row r="14" spans="1:38" ht="17" thickBot="1">
       <c r="A14" s="75" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>209</v>
@@ -4333,7 +4343,7 @@
     </row>
     <row r="15" spans="1:38" ht="17" thickBot="1">
       <c r="A15" s="75" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B15" s="32" t="s">
         <v>209</v>
@@ -17522,13 +17532,13 @@
     </row>
     <row r="2" spans="1:39" ht="16" thickBot="1">
       <c r="A2" s="70" t="s">
-        <v>339</v>
+        <v>403</v>
       </c>
       <c r="B2" s="42" t="s">
         <v>310</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="D2" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17536,7 +17546,7 @@
       </c>
       <c r="E2" s="31" t="str" cm="1">
         <f t="array" ref="E2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F2" s="31" t="str" cm="1">
         <f t="array" ref="F2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -17677,13 +17687,13 @@
     </row>
     <row r="3" spans="1:39" ht="16" thickBot="1">
       <c r="A3" s="71" t="s">
-        <v>340</v>
+        <v>404</v>
       </c>
       <c r="B3" s="42" t="s">
         <v>310</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="D3" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17691,7 +17701,7 @@
       </c>
       <c r="E3" s="31" t="str" cm="1">
         <f t="array" ref="E3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F3" s="31" t="str" cm="1">
         <f t="array" ref="F3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -17832,13 +17842,13 @@
     </row>
     <row r="4" spans="1:39" ht="16" thickBot="1">
       <c r="A4" s="71" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="B4" s="42" t="s">
         <v>310</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="D4" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -17846,7 +17856,7 @@
       </c>
       <c r="E4" s="31" t="str" cm="1">
         <f t="array" ref="E4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F4" s="31" t="str" cm="1">
         <f t="array" ref="F4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -17987,13 +17997,13 @@
     </row>
     <row r="5" spans="1:39" ht="16" thickBot="1">
       <c r="A5" s="71" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="B5" s="42" t="s">
         <v>310</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="D5" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -18001,7 +18011,7 @@
       </c>
       <c r="E5" s="31" t="str" cm="1">
         <f t="array" ref="E5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F5" s="31" t="str" cm="1">
         <f t="array" ref="F5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -18142,13 +18152,13 @@
     </row>
     <row r="6" spans="1:39" ht="16" thickBot="1">
       <c r="A6" s="71" t="s">
-        <v>343</v>
+        <v>407</v>
       </c>
       <c r="B6" s="42" t="s">
         <v>310</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="D6" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -18156,7 +18166,7 @@
       </c>
       <c r="E6" s="31" t="str" cm="1">
         <f t="array" ref="E6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F6" s="31" t="str" cm="1">
         <f t="array" ref="F6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -18297,13 +18307,13 @@
     </row>
     <row r="7" spans="1:39" ht="16" thickBot="1">
       <c r="A7" s="71" t="s">
-        <v>344</v>
+        <v>408</v>
       </c>
       <c r="B7" s="42" t="s">
         <v>310</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="D7" s="40" t="str">
         <f>IF(TestCaseConfig!$B$2="Yes","Yes","No")</f>
@@ -18311,7 +18321,7 @@
       </c>
       <c r="E7" s="31" t="str" cm="1">
         <f t="array" ref="E7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(E$1,dataRowRange,ActualDataRange))</f>
-        <v>CARE</v>
+        <v>Cares</v>
       </c>
       <c r="F7" s="31" t="str" cm="1">
         <f t="array" ref="F7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(F$1,dataRowRange,ActualDataRange))</f>
@@ -18976,7 +18986,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="44" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L2" s="44">
         <v>30</v>
@@ -19088,7 +19098,7 @@
         <v>16</v>
       </c>
       <c r="K3" s="44" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L3" s="44">
         <v>90</v>
@@ -19200,7 +19210,7 @@
         <v>16</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L4" s="44">
         <v>10</v>
@@ -19312,7 +19322,7 @@
         <v>16</v>
       </c>
       <c r="K5" s="44" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L5" s="44">
         <v>30</v>
@@ -19424,7 +19434,7 @@
         <v>16</v>
       </c>
       <c r="K6" s="44" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L6" s="44">
         <v>90</v>
@@ -19536,7 +19546,7 @@
         <v>16</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="L7" s="44">
         <v>10</v>
@@ -23680,7 +23690,7 @@
         <v>186</v>
       </c>
       <c r="K44" s="44" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="L44" s="44">
         <v>10</v>
@@ -23792,7 +23802,7 @@
         <v>187</v>
       </c>
       <c r="K45" s="44" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="L45" s="44">
         <v>10</v>
@@ -23904,7 +23914,7 @@
         <v>188</v>
       </c>
       <c r="K46" s="44" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="L46" s="44">
         <v>10</v>
@@ -24016,7 +24026,7 @@
         <v>186</v>
       </c>
       <c r="K47" s="44" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="L47" s="44">
         <v>10</v>
@@ -24128,7 +24138,7 @@
         <v>187</v>
       </c>
       <c r="K48" s="44" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="L48" s="44">
         <v>10</v>
@@ -24240,7 +24250,7 @@
         <v>188</v>
       </c>
       <c r="K49" s="44" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="L49" s="44">
         <v>10</v>
@@ -32568,13 +32578,13 @@
     <row r="124" spans="1:36" s="61" customFormat="1">
       <c r="A124" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_Domestic</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_Domestic</v>
       </c>
       <c r="B124" s="61" t="s">
         <v>310</v>
       </c>
-      <c r="C124" s="61" t="s">
-        <v>338</v>
+      <c r="C124" s="76" t="s">
+        <v>402</v>
       </c>
       <c r="D124" s="46" t="s">
         <v>125</v>
@@ -32679,13 +32689,13 @@
     <row r="125" spans="1:36" s="61" customFormat="1">
       <c r="A125" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_Domestic</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_Domestic</v>
       </c>
       <c r="B125" s="61" t="s">
         <v>310</v>
       </c>
-      <c r="C125" s="61" t="s">
-        <v>338</v>
+      <c r="C125" s="76" t="s">
+        <v>402</v>
       </c>
       <c r="D125" s="46" t="s">
         <v>125</v>
@@ -32790,13 +32800,13 @@
     <row r="126" spans="1:36" s="61" customFormat="1">
       <c r="A126" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_Domestic</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_Domestic</v>
       </c>
       <c r="B126" s="61" t="s">
         <v>310</v>
       </c>
-      <c r="C126" s="61" t="s">
-        <v>338</v>
+      <c r="C126" s="76" t="s">
+        <v>402</v>
       </c>
       <c r="D126" s="46" t="s">
         <v>125</v>
@@ -32901,13 +32911,13 @@
     <row r="127" spans="1:36" s="61" customFormat="1">
       <c r="A127" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_Adult_International</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_Adult_International</v>
       </c>
       <c r="B127" s="61" t="s">
         <v>310</v>
       </c>
-      <c r="C127" s="61" t="s">
-        <v>338</v>
+      <c r="C127" s="76" t="s">
+        <v>402</v>
       </c>
       <c r="D127" s="46" t="s">
         <v>125</v>
@@ -33012,13 +33022,13 @@
     <row r="128" spans="1:36" s="61" customFormat="1">
       <c r="A128" s="61" t="str">
         <f t="shared" si="1"/>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_ChildInfant_International</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_ChildInfant_International</v>
       </c>
       <c r="B128" s="61" t="s">
         <v>310</v>
       </c>
-      <c r="C128" s="61" t="s">
-        <v>338</v>
+      <c r="C128" s="76" t="s">
+        <v>402</v>
       </c>
       <c r="D128" s="46" t="s">
         <v>125</v>
@@ -33123,13 +33133,13 @@
     <row r="129" spans="1:36" s="61" customFormat="1">
       <c r="A129" s="61" t="str">
         <f t="shared" ref="A129" si="2">_xlfn.CONCAT("createAndConfirmGuidedBooking",SUBSTITUTE(B129," ","_"),"_",SUBSTITUTE(C129," ","_"),"_",SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J129," ",""),"-",""),"/",""),"–",""),"+",""),"°",""),",",""),"_",SUBSTITUTE(AJ129," ","_"))</f>
-        <v>createAndConfirmGuidedBookingHumanRemains_CARE_CrematedRemains_International</v>
+        <v>createAndConfirmGuidedBookingHumanRemains_Cares_CrematedRemains_International</v>
       </c>
       <c r="B129" s="61" t="s">
         <v>310</v>
       </c>
-      <c r="C129" s="61" t="s">
-        <v>338</v>
+      <c r="C129" s="76" t="s">
+        <v>402</v>
       </c>
       <c r="D129" s="46" t="s">
         <v>125</v>
@@ -33233,7 +33243,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL129" xr:uid="{1DAEE888-1773-9E47-9558-1F0A440779BF}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{A27DD8EB-70E3-9343-A2F0-4EC1F414F378}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{B7F22B40-D1E3-41A2-B580-43255BDF4D3A}"/>
@@ -33540,7 +33550,7 @@
     </row>
     <row r="2" spans="1:41" ht="16.5" thickBot="1">
       <c r="A2" s="74" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B2" s="38" t="str" cm="1">
         <f t="array" ref="B2">_xlfn.XLOOKUP($A2,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -33703,7 +33713,7 @@
     </row>
     <row r="3" spans="1:41" ht="16.5" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B3" s="38" t="str" cm="1">
         <f t="array" ref="B3">_xlfn.XLOOKUP($A3,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -33866,7 +33876,7 @@
     </row>
     <row r="4" spans="1:41" ht="16.5" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B4" s="38" t="str" cm="1">
         <f t="array" ref="B4">_xlfn.XLOOKUP($A4,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -34030,7 +34040,7 @@
     </row>
     <row r="5" spans="1:41" ht="16.5" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B5" s="38" t="str" cm="1">
         <f t="array" ref="B5">_xlfn.XLOOKUP($A5,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -34194,7 +34204,7 @@
     </row>
     <row r="6" spans="1:41" ht="16.5" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B6" s="38" t="str" cm="1">
         <f t="array" ref="B6">_xlfn.XLOOKUP($A6,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -34358,7 +34368,7 @@
     </row>
     <row r="7" spans="1:41" ht="16.5" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B7" s="38" t="str" cm="1">
         <f t="array" ref="B7">_xlfn.XLOOKUP($A7,DataColumnRange,_xlfn.XLOOKUP(B$1,dataRowRange,ActualDataRange))</f>
@@ -34521,7 +34531,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D2" location="AdvBkngSTD!A1" display="AdvBkngSTD" xr:uid="{9836EF3A-0C81-384A-B28E-38769E19AD72}"/>
     <hyperlink ref="A1" location="TestCaseConfig!A1" display="TestCases" xr:uid="{B061C974-A2F8-7C4C-A5EC-974E6D31B128}"/>
@@ -34690,7 +34700,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>47</v>
@@ -34841,7 +34851,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>47</v>
@@ -34992,7 +35002,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>47</v>
@@ -35143,7 +35153,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>47</v>
@@ -35294,7 +35304,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>47</v>
@@ -35445,7 +35455,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>47</v>
@@ -35596,7 +35606,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>47</v>
@@ -35747,7 +35757,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>47</v>
@@ -35898,7 +35908,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>47</v>
@@ -36049,7 +36059,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>47</v>
@@ -36344,7 +36354,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>58</v>
@@ -36495,7 +36505,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>58</v>
@@ -36646,7 +36656,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>58</v>
@@ -36797,7 +36807,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>58</v>
@@ -36948,7 +36958,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>58</v>
@@ -37099,7 +37109,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>58</v>
@@ -37250,7 +37260,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>58</v>
@@ -37401,7 +37411,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>58</v>
@@ -37552,7 +37562,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>58</v>
@@ -37703,7 +37713,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>58</v>
@@ -37996,7 +38006,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>44</v>
@@ -38147,7 +38157,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>44</v>
@@ -38298,7 +38308,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>44</v>
@@ -38449,7 +38459,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>44</v>
@@ -38600,7 +38610,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>44</v>
@@ -38751,7 +38761,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>44</v>
@@ -38902,7 +38912,7 @@
     </row>
     <row r="8" spans="1:38" ht="17" thickBot="1">
       <c r="A8" s="75" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>44</v>
@@ -39053,7 +39063,7 @@
     </row>
     <row r="9" spans="1:38" ht="17" thickBot="1">
       <c r="A9" s="75" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>44</v>
@@ -39204,7 +39214,7 @@
     </row>
     <row r="10" spans="1:38" ht="17" thickBot="1">
       <c r="A10" s="75" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>44</v>
@@ -39355,7 +39365,7 @@
     </row>
     <row r="11" spans="1:38" ht="17" thickBot="1">
       <c r="A11" s="75" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>44</v>
@@ -39506,7 +39516,7 @@
     </row>
     <row r="12" spans="1:38" ht="17" thickBot="1">
       <c r="A12" s="75" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>44</v>
@@ -39657,7 +39667,7 @@
     </row>
     <row r="13" spans="1:38" ht="17" thickBot="1">
       <c r="A13" s="75" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>44</v>
@@ -39951,7 +39961,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B2" s="33" t="s">
         <v>87</v>
@@ -40102,7 +40112,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>87</v>
@@ -40253,7 +40263,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>87</v>
@@ -40404,7 +40414,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>87</v>
@@ -40699,7 +40709,7 @@
     </row>
     <row r="2" spans="1:38" ht="17" thickBot="1">
       <c r="A2" s="75" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>89</v>
@@ -40850,7 +40860,7 @@
     </row>
     <row r="3" spans="1:38" ht="17" thickBot="1">
       <c r="A3" s="75" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>89</v>
@@ -41001,7 +41011,7 @@
     </row>
     <row r="4" spans="1:38" ht="17" thickBot="1">
       <c r="A4" s="75" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>89</v>
@@ -41152,7 +41162,7 @@
     </row>
     <row r="5" spans="1:38" ht="17" thickBot="1">
       <c r="A5" s="75" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>89</v>
@@ -41303,7 +41313,7 @@
     </row>
     <row r="6" spans="1:38" ht="17" thickBot="1">
       <c r="A6" s="75" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>89</v>
@@ -41454,7 +41464,7 @@
     </row>
     <row r="7" spans="1:38" ht="17" thickBot="1">
       <c r="A7" s="75" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>89</v>
